--- a/database/event/8048/event_8048_evp_summary.xlsx
+++ b/database/event/8048/event_8048_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8048" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8048" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>1.7342</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4319</v>
+        <v>2.7629</v>
       </c>
       <c r="E2" t="n">
         <v>7.8822</v>
@@ -548,7 +548,7 @@
         <v>1.7073</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3866</v>
+        <v>2.7134</v>
       </c>
       <c r="E3" t="n">
         <v>7.7598</v>
@@ -594,7 +594,7 @@
         <v>1.6069</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2178</v>
+        <v>2.5291</v>
       </c>
       <c r="E4" t="n">
         <v>7.3035</v>
@@ -640,7 +640,7 @@
         <v>1.3147</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7265</v>
+        <v>1.9927</v>
       </c>
       <c r="E5" t="n">
         <v>5.9757</v>
@@ -686,7 +686,7 @@
         <v>1.3026</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7061</v>
+        <v>1.9704</v>
       </c>
       <c r="E6" t="n">
         <v>5.9205</v>
@@ -732,7 +732,7 @@
         <v>1.2804</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6687</v>
+        <v>1.9296</v>
       </c>
       <c r="E7" t="n">
         <v>5.8195</v>
@@ -778,7 +778,7 @@
         <v>1.1797</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4994</v>
+        <v>1.7447</v>
       </c>
       <c r="E8" t="n">
         <v>5.3618</v>
@@ -824,7 +824,7 @@
         <v>1.1735</v>
       </c>
       <c r="D9" t="n">
-        <v>1.489</v>
+        <v>1.7334</v>
       </c>
       <c r="E9" t="n">
         <v>5.3338</v>
@@ -870,7 +870,7 @@
         <v>1.1432</v>
       </c>
       <c r="D10" t="n">
-        <v>1.438</v>
+        <v>1.6777</v>
       </c>
       <c r="E10" t="n">
         <v>5.1961</v>
@@ -916,7 +916,7 @@
         <v>1.1294</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4148</v>
+        <v>1.6524</v>
       </c>
       <c r="E11" t="n">
         <v>5.1334</v>
@@ -962,7 +962,7 @@
         <v>1.1066</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3765</v>
+        <v>1.6106</v>
       </c>
       <c r="E12" t="n">
         <v>5.0298</v>
@@ -1008,7 +1008,7 @@
         <v>1.0228</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2355</v>
+        <v>1.4566</v>
       </c>
       <c r="E13" t="n">
         <v>4.6487</v>
@@ -1054,7 +1054,7 @@
         <v>0.9788</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1615</v>
+        <v>1.3758</v>
       </c>
       <c r="E14" t="n">
         <v>4.4486</v>
@@ -1100,7 +1100,7 @@
         <v>0.9249000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0709</v>
+        <v>1.2769</v>
       </c>
       <c r="E15" t="n">
         <v>4.2039</v>
@@ -1146,7 +1146,7 @@
         <v>0.9213</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0648</v>
+        <v>1.2703</v>
       </c>
       <c r="E16" t="n">
         <v>4.1874</v>
@@ -1192,7 +1192,7 @@
         <v>0.9191</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0611</v>
+        <v>1.2662</v>
       </c>
       <c r="E17" t="n">
         <v>4.1773</v>
@@ -1238,7 +1238,7 @@
         <v>0.86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9618</v>
+        <v>1.1578</v>
       </c>
       <c r="E18" t="n">
         <v>3.909</v>
@@ -1284,7 +1284,7 @@
         <v>0.8321</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9147999999999999</v>
+        <v>1.1064</v>
       </c>
       <c r="E19" t="n">
         <v>3.7819</v>
@@ -1330,7 +1330,7 @@
         <v>0.8168</v>
       </c>
       <c r="D20" t="n">
-        <v>0.889</v>
+        <v>1.0783</v>
       </c>
       <c r="E20" t="n">
         <v>3.7123</v>
@@ -1376,7 +1376,7 @@
         <v>0.8027</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8653999999999999</v>
+        <v>1.0525</v>
       </c>
       <c r="E21" t="n">
         <v>3.6484</v>
@@ -1422,7 +1422,7 @@
         <v>0.7665</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8046</v>
+        <v>0.9861</v>
       </c>
       <c r="E22" t="n">
         <v>3.4841</v>
@@ -1468,7 +1468,7 @@
         <v>0.7252</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7351</v>
+        <v>0.9103</v>
       </c>
       <c r="E23" t="n">
         <v>3.2963</v>
@@ -1514,7 +1514,7 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6724</v>
+        <v>0.8418</v>
       </c>
       <c r="E24" t="n">
         <v>3.1269</v>
@@ -1560,7 +1560,7 @@
         <v>0.6721</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.8127</v>
       </c>
       <c r="E25" t="n">
         <v>3.0547</v>
@@ -1606,7 +1606,7 @@
         <v>0.6703</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6427</v>
+        <v>0.8094</v>
       </c>
       <c r="E26" t="n">
         <v>3.0466</v>
@@ -1652,7 +1652,7 @@
         <v>0.6181</v>
       </c>
       <c r="D27" t="n">
-        <v>0.555</v>
+        <v>0.7136</v>
       </c>
       <c r="E27" t="n">
         <v>2.8095</v>
@@ -1698,7 +1698,7 @@
         <v>0.5576</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532</v>
+        <v>0.6025</v>
       </c>
       <c r="E28" t="n">
         <v>2.5344</v>
@@ -1744,7 +1744,7 @@
         <v>0.5438</v>
       </c>
       <c r="D29" t="n">
-        <v>0.43</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="E29" t="n">
         <v>2.4716</v>
@@ -1790,7 +1790,7 @@
         <v>0.535</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4152</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>2.4317</v>
@@ -1836,7 +1836,7 @@
         <v>0.5328000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4115</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>2.4217</v>
@@ -1882,7 +1882,7 @@
         <v>0.5185999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3877</v>
+        <v>0.5309</v>
       </c>
       <c r="E32" t="n">
         <v>2.3572</v>
@@ -1928,7 +1928,7 @@
         <v>0.4822</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3265</v>
+        <v>0.4641</v>
       </c>
       <c r="E33" t="n">
         <v>2.1919</v>
@@ -1974,7 +1974,7 @@
         <v>0.4469</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2671</v>
+        <v>0.3992</v>
       </c>
       <c r="E34" t="n">
         <v>2.0313</v>
@@ -2020,7 +2020,7 @@
         <v>0.4276</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2347</v>
+        <v>0.3638</v>
       </c>
       <c r="E35" t="n">
         <v>1.9437</v>
@@ -2066,7 +2066,7 @@
         <v>0.419</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2201</v>
+        <v>0.348</v>
       </c>
       <c r="E36" t="n">
         <v>1.9044</v>
@@ -2112,7 +2112,7 @@
         <v>0.4186</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2195</v>
+        <v>0.3473</v>
       </c>
       <c r="E37" t="n">
         <v>1.9028</v>
@@ -2158,7 +2158,7 @@
         <v>0.3958</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1811</v>
+        <v>0.3054</v>
       </c>
       <c r="E38" t="n">
         <v>1.7989</v>
@@ -2204,7 +2204,7 @@
         <v>0.3679</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1342</v>
+        <v>0.2542</v>
       </c>
       <c r="E39" t="n">
         <v>1.6722</v>
@@ -2250,7 +2250,7 @@
         <v>0.306</v>
       </c>
       <c r="D40" t="n">
-        <v>0.03</v>
+        <v>0.1404</v>
       </c>
       <c r="E40" t="n">
         <v>1.3906</v>
@@ -2296,7 +2296,7 @@
         <v>0.2832</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0987</v>
       </c>
       <c r="E41" t="n">
         <v>1.2874</v>
@@ -2342,7 +2342,7 @@
         <v>0.283</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="E42" t="n">
         <v>1.2861</v>
@@ -2388,7 +2388,7 @@
         <v>0.2802</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0134</v>
+        <v>0.0931</v>
       </c>
       <c r="E43" t="n">
         <v>1.2734</v>
@@ -2434,7 +2434,7 @@
         <v>0.2581</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0505</v>
+        <v>0.0525</v>
       </c>
       <c r="E44" t="n">
         <v>1.1729</v>
@@ -2480,7 +2480,7 @@
         <v>0.2553</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0551</v>
+        <v>0.0475</v>
       </c>
       <c r="E45" t="n">
         <v>1.1605</v>
@@ -2526,7 +2526,7 @@
         <v>0.2366</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0866</v>
+        <v>0.0131</v>
       </c>
       <c r="E46" t="n">
         <v>1.0755</v>
@@ -2572,7 +2572,7 @@
         <v>0.1753</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1898</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="E47" t="n">
         <v>0.7966</v>
@@ -2618,7 +2618,7 @@
         <v>0.1579</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2189</v>
+        <v>-0.1314</v>
       </c>
       <c r="E48" t="n">
         <v>0.7178</v>
@@ -2664,7 +2664,7 @@
         <v>0.1534</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2265</v>
+        <v>-0.1397</v>
       </c>
       <c r="E49" t="n">
         <v>0.6973</v>
@@ -2710,7 +2710,7 @@
         <v>0.119</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2845</v>
+        <v>-0.2029</v>
       </c>
       <c r="E50" t="n">
         <v>0.5407</v>
@@ -2756,7 +2756,7 @@
         <v>0.1169</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.288</v>
+        <v>-0.2068</v>
       </c>
       <c r="E51" t="n">
         <v>0.5312</v>
@@ -2802,7 +2802,7 @@
         <v>0.0728</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3621</v>
+        <v>-0.2877</v>
       </c>
       <c r="E52" t="n">
         <v>0.3309</v>
@@ -2848,7 +2848,7 @@
         <v>0.0706</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3657</v>
+        <v>-0.2916</v>
       </c>
       <c r="E53" t="n">
         <v>0.3211</v>
@@ -2894,7 +2894,7 @@
         <v>0.0286</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4365</v>
+        <v>-0.3689</v>
       </c>
       <c r="E54" t="n">
         <v>0.1299</v>
@@ -2940,7 +2940,7 @@
         <v>0.0248</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4428</v>
+        <v>-0.3758</v>
       </c>
       <c r="E55" t="n">
         <v>0.1128</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0047</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4924</v>
+        <v>-0.4299</v>
       </c>
       <c r="E56" t="n">
         <v>-0.0212</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0129</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5062</v>
+        <v>-0.4451</v>
       </c>
       <c r="E57" t="n">
         <v>-0.0587</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0155</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.4498</v>
       </c>
       <c r="E58" t="n">
         <v>-0.07049999999999999</v>
@@ -3124,7 +3124,7 @@
         <v>-0.0338</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5413</v>
+        <v>-0.4834</v>
       </c>
       <c r="E59" t="n">
         <v>-0.1536</v>
@@ -3170,7 +3170,7 @@
         <v>-0.0673</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5976</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3057</v>
@@ -3216,7 +3216,7 @@
         <v>-0.09039999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6365</v>
+        <v>-0.5873</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4108</v>
@@ -3262,7 +3262,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.647</v>
+        <v>-0.5988</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4392</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1458</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7298</v>
+        <v>-0.6891</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6627999999999999</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1543</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.744</v>
+        <v>-0.7047</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7014</v>
@@ -3400,7 +3400,7 @@
         <v>-0.1609</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.755</v>
+        <v>-0.7167</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7311</v>
@@ -3446,7 +3446,7 @@
         <v>-0.1755</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.7437</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7978</v>
@@ -3492,7 +3492,7 @@
         <v>-0.1985</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8183</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9022</v>
@@ -3538,7 +3538,7 @@
         <v>-0.22</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8545</v>
+        <v>-0.8253</v>
       </c>
       <c r="E68" t="n">
         <v>-1</v>
@@ -3584,7 +3584,7 @@
         <v>-0.2408</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8894</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="E69" t="n">
         <v>-1.0943</v>
@@ -3630,7 +3630,7 @@
         <v>-0.3198</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0223</v>
+        <v>-1.0085</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4535</v>
@@ -3676,7 +3676,7 @@
         <v>-0.323</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0278</v>
+        <v>-1.0145</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4683</v>
@@ -3722,7 +3722,7 @@
         <v>-0.3422</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0601</v>
+        <v>-1.0497</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5555</v>
@@ -3768,7 +3768,7 @@
         <v>-0.3429</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0611</v>
+        <v>-1.0509</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5584</v>
@@ -3814,7 +3814,7 @@
         <v>-0.3527</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0777</v>
+        <v>-1.0691</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6033</v>
@@ -3860,7 +3860,7 @@
         <v>-0.3918</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1434</v>
+        <v>-1.1408</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7808</v>
@@ -3952,7 +3952,7 @@
         <v>-0.5063</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.336</v>
+        <v>-1.3511</v>
       </c>
       <c r="E77" t="n">
         <v>-2.3014</v>
@@ -3998,7 +3998,7 @@
         <v>-0.5898</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4765</v>
+        <v>-1.5044</v>
       </c>
       <c r="E78" t="n">
         <v>-2.6809</v>
@@ -4044,7 +4044,7 @@
         <v>-0.6647</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6024</v>
+        <v>-1.6419</v>
       </c>
       <c r="E79" t="n">
         <v>-3.0212</v>
@@ -4090,7 +4090,7 @@
         <v>-0.8601</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.931</v>
+        <v>-2.0006</v>
       </c>
       <c r="E80" t="n">
         <v>-3.9093</v>
@@ -4136,7 +4136,7 @@
         <v>-1.0316</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2193</v>
+        <v>-2.3155</v>
       </c>
       <c r="E81" t="n">
         <v>-4.6886</v>

--- a/database/event/8048/event_8048_evp_summary.xlsx
+++ b/database/event/8048/event_8048_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8822</v>
+        <v>7.8587</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7342</v>
+        <v>1.729</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7629</v>
+        <v>2.687</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8822</v>
+        <v>7.8587</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1551</v>
+        <v>3.1316</v>
       </c>
       <c r="G2" t="n">
         <v>4.7271</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1551</v>
+        <v>3.1316</v>
       </c>
       <c r="I2" t="n">
         <v>3.1846</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7598</v>
+        <v>7.7371</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7073</v>
+        <v>1.7023</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7134</v>
+        <v>2.6386</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7598</v>
+        <v>7.7371</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5158</v>
+        <v>4.4931</v>
       </c>
       <c r="G3" t="n">
         <v>3.244</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7777</v>
+        <v>4.7421</v>
       </c>
       <c r="I3" t="n">
         <v>4.8223</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3035</v>
+        <v>7.2818</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6069</v>
+        <v>1.6021</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5291</v>
+        <v>2.4572</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3035</v>
+        <v>7.2818</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9177</v>
+        <v>2.896</v>
       </c>
       <c r="G4" t="n">
         <v>4.3858</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9177</v>
+        <v>2.896</v>
       </c>
       <c r="I4" t="n">
         <v>2.9449</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9757</v>
+        <v>5.9622</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3147</v>
+        <v>1.3118</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9927</v>
+        <v>1.9314</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9757</v>
+        <v>5.9622</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8134</v>
+        <v>1.7999</v>
       </c>
       <c r="G5" t="n">
         <v>4.1623</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8134</v>
+        <v>1.7999</v>
       </c>
       <c r="I5" t="n">
         <v>1.8303</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9205</v>
+        <v>5.8989</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3026</v>
+        <v>1.2978</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9704</v>
+        <v>1.9062</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9205</v>
+        <v>5.8989</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3588</v>
+        <v>4.3372</v>
       </c>
       <c r="G6" t="n">
         <v>1.5617</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5315</v>
+        <v>4.4977</v>
       </c>
       <c r="I6" t="n">
         <v>4.5738</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8195</v>
+        <v>5.7692</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2804</v>
+        <v>1.2693</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9296</v>
+        <v>1.8545</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8195</v>
+        <v>5.7692</v>
       </c>
       <c r="F7" t="n">
-        <v>4.861</v>
+        <v>4.8107</v>
       </c>
       <c r="G7" t="n">
         <v>0.9585</v>
       </c>
       <c r="H7" t="n">
-        <v>5.319</v>
+        <v>5.2401</v>
       </c>
       <c r="I7" t="n">
         <v>5.4187</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.3618</v>
+        <v>5.3368</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1797</v>
+        <v>1.1742</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7447</v>
+        <v>1.6823</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3618</v>
+        <v>5.3368</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3527</v>
+        <v>3.3277</v>
       </c>
       <c r="G8" t="n">
         <v>2.0091</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3527</v>
+        <v>3.3277</v>
       </c>
       <c r="I8" t="n">
         <v>3.3839</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3338</v>
+        <v>5.2921</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1735</v>
+        <v>1.1643</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7334</v>
+        <v>1.6645</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3338</v>
+        <v>5.2921</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7317</v>
+        <v>3.69</v>
       </c>
       <c r="G9" t="n">
         <v>1.6021</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7317</v>
+        <v>3.69</v>
       </c>
       <c r="I9" t="n">
         <v>3.784</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.1961</v>
+        <v>5.1684</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1432</v>
+        <v>1.1371</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6777</v>
+        <v>1.6152</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1961</v>
+        <v>5.1684</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1961</v>
+        <v>5.1684</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8444</v>
+        <v>5.8009</v>
       </c>
       <c r="I10" t="n">
         <v>5.899</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.1334</v>
+        <v>5.1065</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1294</v>
+        <v>1.1235</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6524</v>
+        <v>1.5905</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1334</v>
+        <v>5.1065</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6207</v>
+        <v>3.5938</v>
       </c>
       <c r="G11" t="n">
         <v>1.5127</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6207</v>
+        <v>3.5938</v>
       </c>
       <c r="I11" t="n">
         <v>3.6545</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.0298</v>
+        <v>5.0051</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1066</v>
+        <v>1.1012</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6106</v>
+        <v>1.5501</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0298</v>
+        <v>5.0051</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3129</v>
+        <v>3.2882</v>
       </c>
       <c r="G12" t="n">
         <v>1.7169</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3129</v>
+        <v>3.2882</v>
       </c>
       <c r="I12" t="n">
         <v>3.3438</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.6487</v>
+        <v>4.6282</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0228</v>
+        <v>1.0183</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4566</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6487</v>
+        <v>4.6282</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7532</v>
+        <v>2.7327</v>
       </c>
       <c r="G13" t="n">
         <v>1.8955</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7532</v>
+        <v>2.7327</v>
       </c>
       <c r="I13" t="n">
         <v>2.7789</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.4486</v>
+        <v>4.4287</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9788</v>
+        <v>0.9744</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3758</v>
+        <v>1.3205</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4486</v>
+        <v>4.4287</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1517</v>
+        <v>4.1318</v>
       </c>
       <c r="G14" t="n">
         <v>0.2969</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2069</v>
+        <v>4.1756</v>
       </c>
       <c r="I14" t="n">
         <v>4.2461</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.2039</v>
+        <v>4.1762</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9188</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2769</v>
+        <v>1.2199</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2039</v>
+        <v>4.1762</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4804</v>
+        <v>2.4527</v>
       </c>
       <c r="G15" t="n">
         <v>1.7235</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4804</v>
+        <v>2.4527</v>
       </c>
       <c r="I15" t="n">
         <v>2.5152</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.1874</v>
+        <v>4.1621</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9213</v>
+        <v>0.9157</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2703</v>
+        <v>1.2143</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1874</v>
+        <v>4.1621</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3986</v>
+        <v>3.3733</v>
       </c>
       <c r="G16" t="n">
         <v>0.7887999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3986</v>
+        <v>3.3733</v>
       </c>
       <c r="I16" t="n">
         <v>3.4303</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.1773</v>
+        <v>4.1522</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9191</v>
+        <v>0.9135</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2662</v>
+        <v>1.2103</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1773</v>
+        <v>4.1522</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2517</v>
+        <v>2.2266</v>
       </c>
       <c r="G17" t="n">
         <v>1.9256</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2517</v>
+        <v>2.2266</v>
       </c>
       <c r="I17" t="n">
         <v>2.2833</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.909</v>
+        <v>3.8912</v>
       </c>
       <c r="C18" t="n">
-        <v>0.86</v>
+        <v>0.8561</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1578</v>
+        <v>1.1063</v>
       </c>
       <c r="E18" t="n">
-        <v>3.909</v>
+        <v>3.8912</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3915</v>
+        <v>2.3737</v>
       </c>
       <c r="G18" t="n">
         <v>1.5175</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3915</v>
+        <v>2.3737</v>
       </c>
       <c r="I18" t="n">
         <v>2.4139</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.7819</v>
+        <v>3.728</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8321</v>
+        <v>0.8202</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1064</v>
+        <v>1.0413</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7819</v>
+        <v>3.728</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6361</v>
+        <v>3.5822</v>
       </c>
       <c r="G19" t="n">
         <v>0.1458</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6361</v>
+        <v>3.5822</v>
       </c>
       <c r="I19" t="n">
         <v>3.7043</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.7123</v>
+        <v>3.6872</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8168</v>
+        <v>0.8112</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0783</v>
+        <v>1.0251</v>
       </c>
       <c r="E20" t="n">
-        <v>3.7123</v>
+        <v>3.6872</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3755</v>
+        <v>3.3504</v>
       </c>
       <c r="G20" t="n">
         <v>0.3368</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3755</v>
+        <v>3.3504</v>
       </c>
       <c r="I20" t="n">
         <v>3.407</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.6484</v>
+        <v>3.6212</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8027</v>
+        <v>0.7967</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0525</v>
+        <v>0.9988</v>
       </c>
       <c r="E21" t="n">
-        <v>3.6484</v>
+        <v>3.6212</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6484</v>
+        <v>3.6212</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6484</v>
+        <v>3.6212</v>
       </c>
       <c r="I21" t="n">
         <v>3.6824</v>
@@ -1422,7 +1422,7 @@
         <v>0.7665</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9861</v>
+        <v>0.9442</v>
       </c>
       <c r="E22" t="n">
         <v>3.4841</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2963</v>
+        <v>3.2718</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7252</v>
+        <v>0.7198</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9103</v>
+        <v>0.8596</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2963</v>
+        <v>3.2718</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2963</v>
+        <v>3.2718</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2963</v>
+        <v>3.2718</v>
       </c>
       <c r="I23" t="n">
         <v>3.3271</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.1269</v>
+        <v>3.1036</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6828</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8418</v>
+        <v>0.7926</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1269</v>
+        <v>3.1036</v>
       </c>
       <c r="F24" t="n">
-        <v>3.1269</v>
+        <v>3.1036</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1269</v>
+        <v>3.1036</v>
       </c>
       <c r="I24" t="n">
         <v>3.1561</v>
@@ -1560,7 +1560,7 @@
         <v>0.6721</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8127</v>
+        <v>0.7731</v>
       </c>
       <c r="E25" t="n">
         <v>3.0547</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.0466</v>
+        <v>3.0228</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6703</v>
+        <v>0.6651</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8094</v>
+        <v>0.7604</v>
       </c>
       <c r="E26" t="n">
-        <v>3.0466</v>
+        <v>3.0228</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2056</v>
+        <v>3.1818</v>
       </c>
       <c r="G26" t="n">
         <v>-0.159</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2056</v>
+        <v>3.1818</v>
       </c>
       <c r="I26" t="n">
         <v>3.2355</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.8095</v>
+        <v>2.8076</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6181</v>
+        <v>0.6177</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7136</v>
+        <v>0.6746</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8095</v>
+        <v>2.8076</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2659</v>
+        <v>0.2639</v>
       </c>
       <c r="G27" t="n">
         <v>2.5436</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2659</v>
+        <v>0.2639</v>
       </c>
       <c r="I27" t="n">
         <v>0.2684</v>
@@ -1698,7 +1698,7 @@
         <v>0.5576</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6025</v>
+        <v>0.5658</v>
       </c>
       <c r="E28" t="n">
         <v>2.5344</v>
@@ -1744,7 +1744,7 @@
         <v>0.5438</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="E29" t="n">
         <v>2.4716</v>
@@ -1790,7 +1790,7 @@
         <v>0.535</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5249</v>
       </c>
       <c r="E30" t="n">
         <v>2.4317</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.4217</v>
+        <v>2.3856</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5249</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5065</v>
       </c>
       <c r="E31" t="n">
-        <v>2.4217</v>
+        <v>2.3856</v>
       </c>
       <c r="F31" t="n">
-        <v>2.4325</v>
+        <v>2.3964</v>
       </c>
       <c r="G31" t="n">
         <v>-0.0108</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4325</v>
+        <v>2.3964</v>
       </c>
       <c r="I31" t="n">
         <v>2.4782</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.3572</v>
+        <v>2.3508</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5172</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5309</v>
+        <v>0.4926</v>
       </c>
       <c r="E32" t="n">
-        <v>2.3572</v>
+        <v>2.3508</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8542</v>
+        <v>0.8478</v>
       </c>
       <c r="G32" t="n">
         <v>1.503</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8542</v>
+        <v>0.8478</v>
       </c>
       <c r="I32" t="n">
         <v>0.8621</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1919</v>
+        <v>2.1756</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4822</v>
+        <v>0.4787</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4641</v>
+        <v>0.4228</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1919</v>
+        <v>2.1756</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1919</v>
+        <v>2.1756</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1919</v>
+        <v>2.1756</v>
       </c>
       <c r="I33" t="n">
         <v>2.2124</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.0313</v>
+        <v>2.012</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4469</v>
+        <v>0.4427</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3992</v>
+        <v>0.3577</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0313</v>
+        <v>2.012</v>
       </c>
       <c r="F34" t="n">
-        <v>2.5977</v>
+        <v>2.5784</v>
       </c>
       <c r="G34" t="n">
         <v>-0.5664</v>
       </c>
       <c r="H34" t="n">
-        <v>2.5977</v>
+        <v>2.5784</v>
       </c>
       <c r="I34" t="n">
         <v>2.622</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.9437</v>
+        <v>1.9292</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4276</v>
+        <v>0.4245</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3638</v>
+        <v>0.3247</v>
       </c>
       <c r="E35" t="n">
-        <v>1.9437</v>
+        <v>1.9292</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9437</v>
+        <v>1.9292</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.9437</v>
+        <v>1.9292</v>
       </c>
       <c r="I35" t="n">
         <v>1.9618</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>Dawy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.9044</v>
+        <v>1.9028</v>
       </c>
       <c r="C36" t="n">
-        <v>0.419</v>
+        <v>0.4186</v>
       </c>
       <c r="D36" t="n">
-        <v>0.348</v>
+        <v>0.3142</v>
       </c>
       <c r="E36" t="n">
-        <v>1.9044</v>
+        <v>1.9028</v>
       </c>
       <c r="F36" t="n">
-        <v>2.9044</v>
+        <v>1.9028</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.9044</v>
+        <v>1.9028</v>
       </c>
       <c r="I36" t="n">
-        <v>2.9589</v>
+        <v>1.9028</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="L36" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.9589</v>
+        <v>1.9028</v>
       </c>
       <c r="N36" t="n">
-        <v>307</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dawy</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.9028</v>
+        <v>1.8613</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4186</v>
+        <v>0.4095</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3473</v>
+        <v>0.2976</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9028</v>
+        <v>1.8613</v>
       </c>
       <c r="F37" t="n">
-        <v>1.9028</v>
+        <v>2.8613</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.9028</v>
+        <v>2.8613</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9028</v>
+        <v>2.9589</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K37" t="n">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M37" t="n">
-        <v>1.9028</v>
+        <v>1.9589</v>
       </c>
       <c r="N37" t="n">
-        <v>207</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>0.3958</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3054</v>
+        <v>0.2728</v>
       </c>
       <c r="E38" t="n">
         <v>1.7989</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.6722</v>
+        <v>1.6457</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3679</v>
+        <v>0.3621</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2542</v>
+        <v>0.2117</v>
       </c>
       <c r="E39" t="n">
-        <v>1.6722</v>
+        <v>1.6457</v>
       </c>
       <c r="F39" t="n">
-        <v>2.3764</v>
+        <v>2.3499</v>
       </c>
       <c r="G39" t="n">
         <v>-0.7042</v>
       </c>
       <c r="H39" t="n">
-        <v>2.3764</v>
+        <v>2.3499</v>
       </c>
       <c r="I39" t="n">
         <v>2.4098</v>
@@ -2250,7 +2250,7 @@
         <v>0.306</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1404</v>
+        <v>0.1101</v>
       </c>
       <c r="E40" t="n">
         <v>1.3906</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.2874</v>
+        <v>1.2861</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2832</v>
+        <v>0.283</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0987</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2874</v>
+        <v>1.2861</v>
       </c>
       <c r="F41" t="n">
-        <v>1.2874</v>
+        <v>0.6118</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.6743</v>
       </c>
       <c r="H41" t="n">
-        <v>1.2874</v>
+        <v>0.6118</v>
       </c>
       <c r="I41" t="n">
-        <v>1.2994</v>
+        <v>0.6118</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.6743</v>
       </c>
       <c r="K41" t="n">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M41" t="n">
-        <v>1.2994</v>
+        <v>1.2861</v>
       </c>
       <c r="N41" t="n">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.2861</v>
+        <v>1.2778</v>
       </c>
       <c r="C42" t="n">
-        <v>0.283</v>
+        <v>0.2811</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0982</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>1.2861</v>
+        <v>1.2778</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6118</v>
+        <v>1.2778</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6743</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6118</v>
+        <v>1.2778</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6118</v>
+        <v>1.2994</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6743</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="L42" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.2861</v>
+        <v>1.2994</v>
       </c>
       <c r="N42" t="n">
-        <v>266</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43">
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2734</v>
+        <v>1.2639</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2802</v>
+        <v>0.2781</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0931</v>
+        <v>0.0596</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2734</v>
+        <v>1.2639</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2734</v>
+        <v>1.2639</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2734</v>
+        <v>1.2639</v>
       </c>
       <c r="I43" t="n">
         <v>1.2853</v>
@@ -2424,93 +2424,93 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1729</v>
+        <v>1.1605</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2581</v>
+        <v>0.2553</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0525</v>
+        <v>0.0184</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1729</v>
+        <v>1.1605</v>
       </c>
       <c r="F44" t="n">
-        <v>2.8783</v>
+        <v>1.1605</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.7054</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.8783</v>
+        <v>1.1605</v>
       </c>
       <c r="I44" t="n">
-        <v>2.9052</v>
+        <v>1.1605</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.7054</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>197</v>
+        <v>44</v>
       </c>
       <c r="L44" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1998</v>
+        <v>1.1605</v>
       </c>
       <c r="N44" t="n">
-        <v>312</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.1605</v>
+        <v>1.1515</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2553</v>
+        <v>0.2533</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0475</v>
+        <v>0.0148</v>
       </c>
       <c r="E45" t="n">
-        <v>1.1605</v>
+        <v>1.1515</v>
       </c>
       <c r="F45" t="n">
-        <v>1.1605</v>
+        <v>2.8569</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1.7054</v>
       </c>
       <c r="H45" t="n">
-        <v>1.1605</v>
+        <v>2.8569</v>
       </c>
       <c r="I45" t="n">
-        <v>1.1605</v>
+        <v>2.9052</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1.7054</v>
       </c>
       <c r="K45" t="n">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M45" t="n">
-        <v>1.1605</v>
+        <v>1.1998</v>
       </c>
       <c r="N45" t="n">
-        <v>44</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.0755</v>
+        <v>1.065</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2366</v>
+        <v>0.2343</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0131</v>
+        <v>-0.0196</v>
       </c>
       <c r="E46" t="n">
-        <v>1.0755</v>
+        <v>1.065</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4163</v>
+        <v>1.4058</v>
       </c>
       <c r="G46" t="n">
         <v>-0.3408</v>
       </c>
       <c r="H46" t="n">
-        <v>1.4163</v>
+        <v>1.4058</v>
       </c>
       <c r="I46" t="n">
         <v>1.4296</v>
@@ -2572,7 +2572,7 @@
         <v>0.1753</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1265</v>
       </c>
       <c r="E47" t="n">
         <v>0.7966</v>
@@ -2618,7 +2618,7 @@
         <v>0.1579</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1314</v>
+        <v>-0.1579</v>
       </c>
       <c r="E48" t="n">
         <v>0.7178</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6973</v>
+        <v>0.6921</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1534</v>
+        <v>0.1523</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1397</v>
+        <v>-0.1682</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6973</v>
+        <v>0.6921</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6973</v>
+        <v>0.6921</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6973</v>
+        <v>0.6921</v>
       </c>
       <c r="I49" t="n">
         <v>0.7038</v>
@@ -2710,7 +2710,7 @@
         <v>0.119</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2029</v>
+        <v>-0.2285</v>
       </c>
       <c r="E50" t="n">
         <v>0.5407</v>
@@ -2756,7 +2756,7 @@
         <v>0.1169</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2068</v>
+        <v>-0.2323</v>
       </c>
       <c r="E51" t="n">
         <v>0.5312</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3309</v>
+        <v>0.3256</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0728</v>
+        <v>0.0716</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2877</v>
+        <v>-0.3142</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3309</v>
+        <v>0.3256</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7106</v>
+        <v>0.7053</v>
       </c>
       <c r="G52" t="n">
         <v>-0.3797</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7106</v>
+        <v>0.7053</v>
       </c>
       <c r="I52" t="n">
         <v>0.7173</v>
@@ -2848,7 +2848,7 @@
         <v>0.0706</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2916</v>
+        <v>-0.316</v>
       </c>
       <c r="E53" t="n">
         <v>0.3211</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1299</v>
+        <v>0.1235</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0286</v>
+        <v>0.0272</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3689</v>
+        <v>-0.3947</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1299</v>
+        <v>0.1235</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8581</v>
+        <v>0.8517</v>
       </c>
       <c r="G54" t="n">
         <v>-0.7282</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8581</v>
+        <v>0.8517</v>
       </c>
       <c r="I54" t="n">
         <v>0.8661</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1128</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0248</v>
+        <v>0.0207</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3758</v>
+        <v>-0.4063</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1128</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>1.6586</v>
+        <v>1.6401</v>
       </c>
       <c r="G55" t="n">
         <v>-1.5458</v>
       </c>
       <c r="H55" t="n">
-        <v>1.6586</v>
+        <v>1.6401</v>
       </c>
       <c r="I55" t="n">
         <v>1.6818</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0047</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4299</v>
+        <v>-0.4524</v>
       </c>
       <c r="E56" t="n">
         <v>-0.0212</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0129</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4451</v>
+        <v>-0.4673</v>
       </c>
       <c r="E57" t="n">
         <v>-0.0587</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0155</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4498</v>
+        <v>-0.472</v>
       </c>
       <c r="E58" t="n">
         <v>-0.07049999999999999</v>
@@ -3124,7 +3124,7 @@
         <v>-0.0338</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4834</v>
+        <v>-0.5051</v>
       </c>
       <c r="E59" t="n">
         <v>-0.1536</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3057</v>
+        <v>-0.3035</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0673</v>
+        <v>-0.0668</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5648</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3057</v>
+        <v>-0.3035</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3057</v>
+        <v>-0.3035</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3057</v>
+        <v>-0.3035</v>
       </c>
       <c r="I60" t="n">
         <v>-0.3086</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4108</v>
+        <v>-0.404</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5873</v>
+        <v>-0.6049</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4108</v>
+        <v>-0.404</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.9119</v>
+        <v>-0.9051</v>
       </c>
       <c r="G61" t="n">
         <v>0.5011</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.9119</v>
+        <v>-0.9051</v>
       </c>
       <c r="I61" t="n">
         <v>-0.9204</v>
@@ -3262,7 +3262,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5988</v>
+        <v>-0.6189</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4392</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1458</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6891</v>
+        <v>-0.708</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6627999999999999</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1543</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7047</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7014</v>
@@ -3400,7 +3400,7 @@
         <v>-0.1609</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7167</v>
+        <v>-0.7352</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7311</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7978</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1755</v>
+        <v>-0.1738</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7437</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7978</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.0734</v>
+        <v>-1.0654</v>
       </c>
       <c r="G66" t="n">
         <v>0.2756</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.0734</v>
+        <v>-1.0654</v>
       </c>
       <c r="I66" t="n">
         <v>-1.0834</v>
@@ -3492,7 +3492,7 @@
         <v>-0.1985</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.8033</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9022</v>
@@ -3538,7 +3538,7 @@
         <v>-0.22</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E68" t="n">
         <v>-1</v>
@@ -3584,7 +3584,7 @@
         <v>-0.2408</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.8799</v>
       </c>
       <c r="E69" t="n">
         <v>-1.0943</v>
@@ -3630,7 +3630,7 @@
         <v>-0.3198</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0085</v>
+        <v>-1.023</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4535</v>
@@ -3676,7 +3676,7 @@
         <v>-0.323</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0145</v>
+        <v>-1.0289</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4683</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.5555</v>
+        <v>-1.5406</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3422</v>
+        <v>-0.339</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0497</v>
+        <v>-1.0577</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.5555</v>
+        <v>-1.5406</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0074</v>
+        <v>-0.9925</v>
       </c>
       <c r="G72" t="n">
         <v>-0.5481</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0074</v>
+        <v>-0.9925</v>
       </c>
       <c r="I72" t="n">
         <v>-1.0263</v>
@@ -3768,7 +3768,7 @@
         <v>-0.3429</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0509</v>
+        <v>-1.0648</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5584</v>
@@ -3814,7 +3814,7 @@
         <v>-0.3527</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0691</v>
+        <v>-1.0827</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6033</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.7808</v>
+        <v>-1.766</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.3918</v>
+        <v>-0.3885</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1408</v>
+        <v>-1.1475</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.7808</v>
+        <v>-1.766</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.9791</v>
+        <v>-1.9644</v>
       </c>
       <c r="G75" t="n">
         <v>0.1984</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.9791</v>
+        <v>-1.9644</v>
       </c>
       <c r="I75" t="n">
         <v>-1.9976</v>
@@ -3906,7 +3906,7 @@
         <v>-0.409</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1723</v>
+        <v>-1.1845</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8589</v>
@@ -3952,7 +3952,7 @@
         <v>-0.5063</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3511</v>
+        <v>-1.3608</v>
       </c>
       <c r="E77" t="n">
         <v>-2.3014</v>
@@ -3998,7 +3998,7 @@
         <v>-0.5898</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5044</v>
+        <v>-1.512</v>
       </c>
       <c r="E78" t="n">
         <v>-2.6809</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.0212</v>
+        <v>-3.0004</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6647</v>
+        <v>-0.6601</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6419</v>
+        <v>-1.6393</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.0212</v>
+        <v>-3.0004</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.787</v>
+        <v>-2.7662</v>
       </c>
       <c r="G79" t="n">
         <v>-0.2342</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.787</v>
+        <v>-2.7662</v>
       </c>
       <c r="I79" t="n">
         <v>-2.813</v>
@@ -4090,7 +4090,7 @@
         <v>-0.8601</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.0006</v>
+        <v>-2.0014</v>
       </c>
       <c r="E80" t="n">
         <v>-3.9093</v>
@@ -4136,7 +4136,7 @@
         <v>-1.0316</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.3155</v>
+        <v>-2.3118</v>
       </c>
       <c r="E81" t="n">
         <v>-4.6886</v>

--- a/database/event/8048/event_8048_evp_summary.xlsx
+++ b/database/event/8048/event_8048_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9794</v>
+        <v>8.0733</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7556</v>
+        <v>1.7762</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0082</v>
+        <v>2.9923</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9794</v>
+        <v>8.0733</v>
       </c>
       <c r="F2" t="n">
-        <v>3.386</v>
+        <v>3.3911</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5934</v>
+        <v>4.5753</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6859</v>
+        <v>4.6971</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9305</v>
+        <v>4.9423</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5934</v>
+        <v>4.5753</v>
       </c>
       <c r="K2" t="n">
         <v>131</v>
@@ -529,7 +529,7 @@
         <v>188</v>
       </c>
       <c r="M2" t="n">
-        <v>9.523900000000001</v>
+        <v>9.517600000000002</v>
       </c>
       <c r="N2" t="n">
         <v>319</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3138</v>
+        <v>7.4133</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6091</v>
+        <v>1.631</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7052</v>
+        <v>2.6975</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3138</v>
+        <v>7.4133</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1169</v>
+        <v>3.1082</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1969</v>
+        <v>4.1693</v>
       </c>
       <c r="H3" t="n">
-        <v>4.097</v>
+        <v>4.078</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3109</v>
+        <v>4.2909</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1969</v>
+        <v>4.1693</v>
       </c>
       <c r="K3" t="n">
         <v>131</v>
@@ -575,7 +575,7 @@
         <v>188</v>
       </c>
       <c r="M3" t="n">
-        <v>8.5078</v>
+        <v>8.4602</v>
       </c>
       <c r="N3" t="n">
         <v>319</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.2112</v>
+        <v>7.3741</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5866</v>
+        <v>1.6224</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6585</v>
+        <v>2.68</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2112</v>
+        <v>7.3741</v>
       </c>
       <c r="F4" t="n">
         <v>4.0025</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7151</v>
+        <v>5.725</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2574</v>
+        <v>1.2596</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9774</v>
+        <v>1.9434</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7151</v>
+        <v>5.725</v>
       </c>
       <c r="F5" t="n">
         <v>1.9576</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7575</v>
+        <v>3.7578</v>
       </c>
       <c r="H5" t="n">
         <v>1.9576</v>
@@ -658,7 +658,7 @@
         <v>2.0598</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7575</v>
+        <v>3.7578</v>
       </c>
       <c r="K5" t="n">
         <v>131</v>
@@ -667,7 +667,7 @@
         <v>188</v>
       </c>
       <c r="M5" t="n">
-        <v>5.817299999999999</v>
+        <v>5.817600000000001</v>
       </c>
       <c r="N5" t="n">
         <v>319</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.146</v>
+        <v>5.3215</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1322</v>
+        <v>1.1708</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7184</v>
+        <v>1.7632</v>
       </c>
       <c r="E6" t="n">
-        <v>5.146</v>
+        <v>5.3215</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8214</v>
+        <v>3.839</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3246</v>
+        <v>1.3242</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6388</v>
+        <v>5.6773</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9332</v>
+        <v>5.9737</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3246</v>
+        <v>1.3242</v>
       </c>
       <c r="K6" t="n">
         <v>280</v>
@@ -713,7 +713,7 @@
         <v>62</v>
       </c>
       <c r="M6" t="n">
-        <v>7.2578</v>
+        <v>7.2979</v>
       </c>
       <c r="N6" t="n">
         <v>342</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.1104</v>
+        <v>5.166</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1244</v>
+        <v>1.1366</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7022</v>
+        <v>1.6937</v>
       </c>
       <c r="E7" t="n">
-        <v>5.1104</v>
+        <v>5.166</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0433</v>
+        <v>3.0513</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0671</v>
+        <v>2.0676</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9359</v>
+        <v>3.9533</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1414</v>
+        <v>4.1597</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0671</v>
+        <v>2.0676</v>
       </c>
       <c r="K7" t="n">
         <v>131</v>
@@ -759,7 +759,7 @@
         <v>188</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2085</v>
+        <v>6.2273</v>
       </c>
       <c r="N7" t="n">
         <v>319</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8659</v>
+        <v>4.9043</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0706</v>
+        <v>1.079</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5909</v>
+        <v>1.5768</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8659</v>
+        <v>4.9043</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8031</v>
+        <v>2.8029</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0628</v>
+        <v>2.0635</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4101</v>
+        <v>3.4098</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5881</v>
+        <v>3.5878</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0628</v>
+        <v>2.0635</v>
       </c>
       <c r="K8" t="n">
         <v>131</v>
@@ -805,7 +805,7 @@
         <v>188</v>
       </c>
       <c r="M8" t="n">
-        <v>5.6509</v>
+        <v>5.6513</v>
       </c>
       <c r="N8" t="n">
         <v>319</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.7429</v>
+        <v>4.9039</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0435</v>
+        <v>1.0789</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5349</v>
+        <v>1.5766</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7429</v>
+        <v>4.9039</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0215</v>
+        <v>3.0376</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7214</v>
+        <v>1.7205</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8882</v>
+        <v>3.9234</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1966</v>
+        <v>4.2346</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7214</v>
+        <v>1.7205</v>
       </c>
       <c r="K9" t="n">
         <v>276</v>
@@ -851,7 +851,7 @@
         <v>120</v>
       </c>
       <c r="M9" t="n">
-        <v>5.918</v>
+        <v>5.9551</v>
       </c>
       <c r="N9" t="n">
         <v>396</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.6668</v>
+        <v>4.9013</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0268</v>
+        <v>1.0784</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5002</v>
+        <v>1.5755</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6668</v>
+        <v>4.9013</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6718</v>
+        <v>3.6615</v>
       </c>
       <c r="G10" t="n">
-        <v>0.995</v>
+        <v>0.9525</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3115</v>
+        <v>5.289</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8805</v>
+        <v>5.8556</v>
       </c>
       <c r="J10" t="n">
-        <v>0.995</v>
+        <v>0.9525</v>
       </c>
       <c r="K10" t="n">
         <v>254</v>
@@ -897,7 +897,7 @@
         <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>6.8755</v>
+        <v>6.8081</v>
       </c>
       <c r="N10" t="n">
         <v>307</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.6116</v>
+        <v>4.6443</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0146</v>
+        <v>1.0218</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4751</v>
+        <v>1.4607</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6116</v>
+        <v>4.6443</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1004</v>
+        <v>3.1108</v>
       </c>
       <c r="G11" t="n">
         <v>1.5112</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0608</v>
+        <v>4.0836</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2728</v>
+        <v>4.2968</v>
       </c>
       <c r="J11" t="n">
         <v>1.5112</v>
@@ -943,7 +943,7 @@
         <v>195</v>
       </c>
       <c r="M11" t="n">
-        <v>5.784000000000001</v>
+        <v>5.808</v>
       </c>
       <c r="N11" t="n">
         <v>345</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.5199</v>
+        <v>4.6152</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9944</v>
+        <v>1.0154</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4333</v>
+        <v>1.4477</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5199</v>
+        <v>4.6152</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0928</v>
+        <v>3.1026</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4271</v>
+        <v>1.4266</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0443</v>
+        <v>4.0658</v>
       </c>
       <c r="I12" t="n">
-        <v>4.365</v>
+        <v>4.3882</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4271</v>
+        <v>1.4266</v>
       </c>
       <c r="K12" t="n">
         <v>276</v>
@@ -989,7 +989,7 @@
         <v>120</v>
       </c>
       <c r="M12" t="n">
-        <v>5.7921</v>
+        <v>5.8148</v>
       </c>
       <c r="N12" t="n">
         <v>396</v>
@@ -998,507 +998,507 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.2311</v>
+        <v>4.2336</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9314</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3019</v>
+        <v>1.2772</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2311</v>
+        <v>4.2336</v>
       </c>
       <c r="F13" t="n">
-        <v>2.419</v>
+        <v>2.4456</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8121</v>
+        <v>1.5685</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5694</v>
+        <v>2.6278</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7732</v>
+        <v>2.765</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8121</v>
+        <v>1.5685</v>
       </c>
       <c r="K13" t="n">
-        <v>276</v>
+        <v>150</v>
       </c>
       <c r="L13" t="n">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5853</v>
+        <v>4.3335</v>
       </c>
       <c r="N13" t="n">
-        <v>396</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.0802</v>
+        <v>4.2309</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2332</v>
+        <v>1.276</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0802</v>
+        <v>4.2309</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8371</v>
+        <v>2.4182</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2431</v>
+        <v>1.8119</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4845</v>
+        <v>2.5677</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6664</v>
+        <v>2.7714</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2431</v>
+        <v>1.8119</v>
       </c>
       <c r="K14" t="n">
-        <v>197</v>
+        <v>276</v>
       </c>
       <c r="L14" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="M14" t="n">
-        <v>4.9095</v>
+        <v>4.583299999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>312</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Banjo</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0314</v>
+        <v>4.1622</v>
       </c>
       <c r="C15" t="n">
-        <v>0.887</v>
+        <v>0.9157</v>
       </c>
       <c r="D15" t="n">
-        <v>1.211</v>
+        <v>1.2453</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0314</v>
+        <v>4.1622</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0314</v>
+        <v>2.8409</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.2435</v>
       </c>
       <c r="H15" t="n">
-        <v>6.0985</v>
+        <v>3.4929</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4169</v>
+        <v>3.6752</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.2435</v>
       </c>
       <c r="K15" t="n">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M15" t="n">
-        <v>6.4169</v>
+        <v>4.918699999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.0142</v>
+        <v>4.1569</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8832</v>
+        <v>0.9146</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2031</v>
+        <v>1.243</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0142</v>
+        <v>4.1569</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4456</v>
+        <v>4.0153</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5685</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6278</v>
+        <v>6.0632</v>
       </c>
       <c r="I16" t="n">
-        <v>2.765</v>
+        <v>6.3797</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5685</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="L16" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3335</v>
+        <v>6.3797</v>
       </c>
       <c r="N16" t="n">
-        <v>345</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>Banjo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.0136</v>
+        <v>3.9788</v>
       </c>
       <c r="C17" t="n">
-        <v>0.883</v>
+        <v>0.8754</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2029</v>
+        <v>1.1634</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0136</v>
+        <v>3.9788</v>
       </c>
       <c r="F17" t="n">
-        <v>4.0136</v>
+        <v>4.0317</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6.0595</v>
+        <v>6.0992</v>
       </c>
       <c r="I17" t="n">
-        <v>6.3758</v>
+        <v>6.4176</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.3758</v>
+        <v>6.4176</v>
       </c>
       <c r="N17" t="n">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>kl1m</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.6541</v>
+        <v>3.9123</v>
       </c>
       <c r="C18" t="n">
-        <v>0.804</v>
+        <v>0.8608</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0392</v>
+        <v>1.1337</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6541</v>
+        <v>3.9123</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8801</v>
+        <v>3.3284</v>
       </c>
       <c r="G18" t="n">
-        <v>0.774</v>
+        <v>0.304</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5787</v>
+        <v>4.56</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7656</v>
+        <v>4.798</v>
       </c>
       <c r="J18" t="n">
-        <v>0.774</v>
+        <v>0.304</v>
       </c>
       <c r="K18" t="n">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="L18" t="n">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5396</v>
+        <v>5.102</v>
       </c>
       <c r="N18" t="n">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kl1m</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6209</v>
+        <v>3.7954</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7966</v>
+        <v>0.835</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0241</v>
+        <v>1.0815</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6209</v>
+        <v>3.7954</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3169</v>
+        <v>2.8799</v>
       </c>
       <c r="G19" t="n">
-        <v>0.304</v>
+        <v>0.7744</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5347</v>
+        <v>3.5782</v>
       </c>
       <c r="I19" t="n">
-        <v>4.7714</v>
+        <v>3.765</v>
       </c>
       <c r="J19" t="n">
-        <v>0.304</v>
+        <v>0.7744</v>
       </c>
       <c r="K19" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="L19" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="M19" t="n">
-        <v>5.0754</v>
+        <v>4.539400000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>292</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3895</v>
+        <v>3.6197</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7457</v>
+        <v>0.7964</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9188</v>
+        <v>1.003</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3895</v>
+        <v>3.6197</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2691</v>
+        <v>3.2131</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1204</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.43</v>
+        <v>4.3075</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6613</v>
+        <v>4.3075</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1204</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L20" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.7817</v>
+        <v>4.3075</v>
       </c>
       <c r="N20" t="n">
-        <v>292</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.3528</v>
+        <v>3.5793</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7377</v>
+        <v>0.7875</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9021</v>
+        <v>0.985</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3528</v>
+        <v>3.5793</v>
       </c>
       <c r="F21" t="n">
-        <v>2.877</v>
+        <v>3.2346</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4758</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5718</v>
+        <v>4.3546</v>
       </c>
       <c r="I21" t="n">
-        <v>3.7583</v>
+        <v>4.3546</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4758</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>280</v>
+        <v>212</v>
       </c>
       <c r="L21" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2341</v>
+        <v>4.3546</v>
       </c>
       <c r="N21" t="n">
-        <v>342</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.2346</v>
+        <v>3.5383</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7117</v>
+        <v>0.7785</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.9667</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2346</v>
+        <v>3.5383</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2346</v>
+        <v>2.8766</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.4757</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3545</v>
+        <v>3.5711</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3545</v>
+        <v>3.7575</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.4757</v>
       </c>
       <c r="K22" t="n">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3545</v>
+        <v>4.2332</v>
       </c>
       <c r="N22" t="n">
-        <v>212</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2134</v>
+        <v>3.4233</v>
       </c>
       <c r="C23" t="n">
-        <v>0.707</v>
+        <v>0.7532</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8386</v>
+        <v>0.9153</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2134</v>
+        <v>3.4233</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2134</v>
+        <v>3.2824</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1204</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3081</v>
+        <v>4.4593</v>
       </c>
       <c r="I23" t="n">
-        <v>4.3081</v>
+        <v>4.6921</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.1204</v>
       </c>
       <c r="K23" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3081</v>
+        <v>4.8125</v>
       </c>
       <c r="N23" t="n">
-        <v>231</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.1985</v>
+        <v>3.3024</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7037</v>
+        <v>0.7266</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8318</v>
+        <v>0.8613</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1985</v>
+        <v>3.3024</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8043</v>
+        <v>2.8041</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3942</v>
+        <v>0.3946</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4127</v>
+        <v>3.4124</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7783</v>
+        <v>3.778</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3942</v>
+        <v>0.3946</v>
       </c>
       <c r="K24" t="n">
         <v>254</v>
@@ -1541,7 +1541,7 @@
         <v>53</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1725</v>
+        <v>4.1726</v>
       </c>
       <c r="N24" t="n">
         <v>307</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>Matheos</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.1565</v>
+        <v>3.2629</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6945</v>
+        <v>0.7179</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8127</v>
+        <v>0.8436</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1565</v>
+        <v>3.2629</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5685</v>
+        <v>3.1185</v>
       </c>
       <c r="G25" t="n">
-        <v>2.588</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5685</v>
+        <v>4.1004</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5982</v>
+        <v>4.3145</v>
       </c>
       <c r="J25" t="n">
-        <v>2.588</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="L25" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1862</v>
+        <v>4.3145</v>
       </c>
       <c r="N25" t="n">
-        <v>345</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matheos</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.1184</v>
+        <v>3.0931</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6861</v>
+        <v>0.6805</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7954</v>
+        <v>0.7678</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1184</v>
+        <v>3.0931</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1184</v>
+        <v>0.5685</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.563</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1003</v>
+        <v>0.5685</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3143</v>
+        <v>0.5982</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.563</v>
       </c>
       <c r="K26" t="n">
-        <v>286</v>
+        <v>150</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="M26" t="n">
-        <v>4.3143</v>
+        <v>3.1612</v>
       </c>
       <c r="N26" t="n">
-        <v>286</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.9362</v>
+        <v>2.9067</v>
       </c>
       <c r="C27" t="n">
-        <v>0.646</v>
+        <v>0.6395</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7124</v>
+        <v>0.6845</v>
       </c>
       <c r="E27" t="n">
-        <v>2.9362</v>
+        <v>2.9067</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9362</v>
+        <v>2.9359</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7015</v>
+        <v>3.7008</v>
       </c>
       <c r="I27" t="n">
-        <v>3.7015</v>
+        <v>3.7008</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7015</v>
+        <v>3.7008</v>
       </c>
       <c r="N27" t="n">
         <v>151</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8368</v>
+        <v>2.7566</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6241</v>
+        <v>0.6065</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6672</v>
+        <v>0.6175</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8368</v>
+        <v>2.7566</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4799</v>
+        <v>1.4792</v>
       </c>
       <c r="G28" t="n">
-        <v>1.3569</v>
+        <v>1.3431</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4799</v>
+        <v>1.4792</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5571</v>
+        <v>1.5565</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3569</v>
+        <v>1.3431</v>
       </c>
       <c r="K28" t="n">
         <v>197</v>
@@ -1725,7 +1725,7 @@
         <v>115</v>
       </c>
       <c r="M28" t="n">
-        <v>2.914</v>
+        <v>2.8996</v>
       </c>
       <c r="N28" t="n">
         <v>312</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>Dawy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.8153</v>
+        <v>2.7498</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6194</v>
+        <v>0.605</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6574</v>
+        <v>0.6145</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8153</v>
+        <v>2.7498</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8153</v>
+        <v>2.3575</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4369</v>
+        <v>2.4348</v>
       </c>
       <c r="I29" t="n">
-        <v>3.6163</v>
+        <v>2.4348</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6163</v>
+        <v>2.4348</v>
       </c>
       <c r="N29" t="n">
-        <v>286</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.6131</v>
+        <v>2.7225</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5749</v>
+        <v>0.599</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5653</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>2.6131</v>
+        <v>2.7225</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6131</v>
+        <v>2.4678</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="H30" t="n">
-        <v>2.9943</v>
+        <v>2.6763</v>
       </c>
       <c r="I30" t="n">
-        <v>2.9943</v>
+        <v>2.6763</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="K30" t="n">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M30" t="n">
-        <v>2.9943</v>
+        <v>2.7753</v>
       </c>
       <c r="N30" t="n">
-        <v>212</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.6074</v>
+        <v>2.6748</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5737</v>
+        <v>0.5885</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5627</v>
+        <v>0.581</v>
       </c>
       <c r="E31" t="n">
-        <v>2.6074</v>
+        <v>2.6748</v>
       </c>
       <c r="F31" t="n">
-        <v>2.7737</v>
+        <v>2.7809</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1663</v>
+        <v>-0.1468</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3458</v>
+        <v>3.3616</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6112</v>
+        <v>3.6282</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1663</v>
+        <v>-0.1468</v>
       </c>
       <c r="K31" t="n">
         <v>276</v>
@@ -1863,7 +1863,7 @@
         <v>120</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4449</v>
+        <v>3.4814</v>
       </c>
       <c r="N31" t="n">
         <v>396</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.5665</v>
+        <v>2.6617</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5647</v>
+        <v>0.5856</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5441</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5665</v>
+        <v>2.6617</v>
       </c>
       <c r="F32" t="n">
-        <v>2.4675</v>
+        <v>2.8154</v>
       </c>
       <c r="G32" t="n">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.6757</v>
+        <v>3.4371</v>
       </c>
       <c r="I32" t="n">
-        <v>2.6757</v>
+        <v>3.6165</v>
       </c>
       <c r="J32" t="n">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="L32" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.7747</v>
+        <v>3.6165</v>
       </c>
       <c r="N32" t="n">
-        <v>266</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.5018</v>
+        <v>2.6207</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5504</v>
+        <v>0.5766</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5147</v>
+        <v>0.5568</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5018</v>
+        <v>2.6207</v>
       </c>
       <c r="F33" t="n">
-        <v>2.4367</v>
+        <v>2.4366</v>
       </c>
       <c r="G33" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0649</v>
       </c>
       <c r="H33" t="n">
-        <v>2.6083</v>
+        <v>2.6079</v>
       </c>
       <c r="I33" t="n">
-        <v>2.8877</v>
+        <v>2.8873</v>
       </c>
       <c r="J33" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0649</v>
       </c>
       <c r="K33" t="n">
         <v>254</v>
@@ -1955,7 +1955,7 @@
         <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9528</v>
+        <v>2.9522</v>
       </c>
       <c r="N33" t="n">
         <v>307</v>
@@ -1964,124 +1964,124 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.4346</v>
+        <v>2.5694</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5356</v>
+        <v>0.5653</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4841</v>
+        <v>0.5339</v>
       </c>
       <c r="E34" t="n">
-        <v>2.4346</v>
+        <v>2.5694</v>
       </c>
       <c r="F34" t="n">
-        <v>2.4346</v>
+        <v>2.6132</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.6036</v>
+        <v>2.9946</v>
       </c>
       <c r="I34" t="n">
-        <v>2.7395</v>
+        <v>2.9946</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>268</v>
+        <v>212</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.7395</v>
+        <v>2.9946</v>
       </c>
       <c r="N34" t="n">
-        <v>268</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dawy</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.3581</v>
+        <v>2.4348</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5188</v>
+        <v>0.5357</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4493</v>
+        <v>0.4738</v>
       </c>
       <c r="E35" t="n">
-        <v>2.3581</v>
+        <v>2.4348</v>
       </c>
       <c r="F35" t="n">
-        <v>2.3581</v>
+        <v>2.1651</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.4363</v>
+        <v>2.1651</v>
       </c>
       <c r="I35" t="n">
-        <v>2.4363</v>
+        <v>2.1651</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.4363</v>
+        <v>2.1651</v>
       </c>
       <c r="N35" t="n">
-        <v>207</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.3354</v>
+        <v>2.3947</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5138</v>
+        <v>0.5269</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4389</v>
+        <v>0.4558</v>
       </c>
       <c r="E36" t="n">
-        <v>2.3354</v>
+        <v>2.3947</v>
       </c>
       <c r="F36" t="n">
-        <v>2.3354</v>
+        <v>2.4345</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3865</v>
+        <v>2.6034</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5111</v>
+        <v>2.7393</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.5111</v>
+        <v>2.7393</v>
       </c>
       <c r="N36" t="n">
         <v>268</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.3229</v>
+        <v>2.3835</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5111</v>
+        <v>0.5244</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4332</v>
+        <v>0.4508</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3229</v>
+        <v>2.3835</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3229</v>
+        <v>2.318</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3591</v>
+        <v>2.3485</v>
       </c>
       <c r="I37" t="n">
-        <v>2.4823</v>
+        <v>2.4711</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.4823</v>
+        <v>2.4711</v>
       </c>
       <c r="N37" t="n">
         <v>286</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.3125</v>
+        <v>2.3598</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5088</v>
+        <v>0.5192</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4285</v>
+        <v>0.4403</v>
       </c>
       <c r="E38" t="n">
-        <v>2.3125</v>
+        <v>2.3598</v>
       </c>
       <c r="F38" t="n">
         <v>2.5121</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1996</v>
+        <v>-0.1993</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7733</v>
+        <v>2.7732</v>
       </c>
       <c r="I38" t="n">
-        <v>2.9181</v>
+        <v>2.918</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1996</v>
+        <v>-0.1993</v>
       </c>
       <c r="K38" t="n">
         <v>197</v>
@@ -2185,7 +2185,7 @@
         <v>115</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7185</v>
+        <v>2.7187</v>
       </c>
       <c r="N38" t="n">
         <v>312</v>
@@ -2194,231 +2194,231 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.2199</v>
+        <v>2.3365</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4884</v>
+        <v>0.5141</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3863</v>
+        <v>0.4298</v>
       </c>
       <c r="E39" t="n">
-        <v>2.2199</v>
+        <v>2.3365</v>
       </c>
       <c r="F39" t="n">
-        <v>2.2948</v>
+        <v>2.3352</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.2978</v>
+        <v>2.3861</v>
       </c>
       <c r="I39" t="n">
-        <v>2.4177</v>
+        <v>2.5107</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="L39" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.3428</v>
+        <v>2.5107</v>
       </c>
       <c r="N39" t="n">
-        <v>342</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.1908</v>
+        <v>2.2936</v>
       </c>
       <c r="C40" t="n">
-        <v>0.482</v>
+        <v>0.5046</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3731</v>
+        <v>0.4107</v>
       </c>
       <c r="E40" t="n">
-        <v>2.1908</v>
+        <v>2.2936</v>
       </c>
       <c r="F40" t="n">
-        <v>2.8661</v>
+        <v>2.2994</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6753</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5481</v>
+        <v>2.3078</v>
       </c>
       <c r="I40" t="n">
-        <v>3.9282</v>
+        <v>2.4283</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6753</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="L40" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2529</v>
+        <v>2.353</v>
       </c>
       <c r="N40" t="n">
-        <v>307</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.1654</v>
+        <v>2.2208</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4764</v>
+        <v>0.4886</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3615</v>
+        <v>0.3782</v>
       </c>
       <c r="E41" t="n">
-        <v>2.1654</v>
+        <v>2.2208</v>
       </c>
       <c r="F41" t="n">
-        <v>2.1654</v>
+        <v>2.8749</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.6661</v>
       </c>
       <c r="H41" t="n">
-        <v>2.1654</v>
+        <v>3.5672</v>
       </c>
       <c r="I41" t="n">
-        <v>2.1654</v>
+        <v>3.9494</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.6661</v>
       </c>
       <c r="K41" t="n">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>2.1654</v>
+        <v>3.2833</v>
       </c>
       <c r="N41" t="n">
-        <v>151</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ro1f</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.1576</v>
+        <v>2.1646</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4747</v>
+        <v>0.4762</v>
       </c>
       <c r="D42" t="n">
-        <v>0.358</v>
+        <v>0.3531</v>
       </c>
       <c r="E42" t="n">
-        <v>2.1576</v>
+        <v>2.1646</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5231</v>
+        <v>2.0809</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.3655</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.7974</v>
+        <v>2.0809</v>
       </c>
       <c r="I42" t="n">
-        <v>2.7974</v>
+        <v>2.1895</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.3655</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="L42" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.4319</v>
+        <v>2.1895</v>
       </c>
       <c r="N42" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>Ro1f</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.081</v>
+        <v>2.1626</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4578</v>
+        <v>0.4758</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3231</v>
+        <v>0.3522</v>
       </c>
       <c r="E43" t="n">
-        <v>2.081</v>
+        <v>2.1626</v>
       </c>
       <c r="F43" t="n">
-        <v>2.081</v>
+        <v>2.5232</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.3655</v>
       </c>
       <c r="H43" t="n">
-        <v>2.081</v>
+        <v>2.7975</v>
       </c>
       <c r="I43" t="n">
-        <v>2.1896</v>
+        <v>2.7975</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.3655</v>
       </c>
       <c r="K43" t="n">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M43" t="n">
-        <v>2.1896</v>
+        <v>2.432</v>
       </c>
       <c r="N43" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.8923</v>
+        <v>1.935</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4163</v>
+        <v>0.4257</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2372</v>
+        <v>0.2505</v>
       </c>
       <c r="E44" t="n">
-        <v>1.8923</v>
+        <v>1.935</v>
       </c>
       <c r="F44" t="n">
-        <v>1.8923</v>
+        <v>1.8915</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.8923</v>
+        <v>1.8915</v>
       </c>
       <c r="I44" t="n">
-        <v>1.8923</v>
+        <v>1.8915</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.8923</v>
+        <v>1.8915</v>
       </c>
       <c r="N44" t="n">
         <v>231</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.6827</v>
+        <v>1.8545</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3702</v>
+        <v>0.408</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1418</v>
+        <v>0.2145</v>
       </c>
       <c r="E45" t="n">
-        <v>1.6827</v>
+        <v>1.8545</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9344</v>
+        <v>0.9351</v>
       </c>
       <c r="G45" t="n">
         <v>0.7483</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9344</v>
+        <v>0.9351</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9344</v>
+        <v>0.9351</v>
       </c>
       <c r="J45" t="n">
         <v>0.7483</v>
@@ -2507,7 +2507,7 @@
         <v>66</v>
       </c>
       <c r="M45" t="n">
-        <v>1.6827</v>
+        <v>1.6834</v>
       </c>
       <c r="N45" t="n">
         <v>266</v>
@@ -2516,277 +2516,277 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.6678</v>
+        <v>1.5804</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3669</v>
+        <v>0.3477</v>
       </c>
       <c r="D46" t="n">
-        <v>0.135</v>
+        <v>0.0921</v>
       </c>
       <c r="E46" t="n">
-        <v>1.6678</v>
+        <v>1.5804</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6678</v>
+        <v>1.3415</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.6678</v>
+        <v>1.3415</v>
       </c>
       <c r="I46" t="n">
-        <v>1.6678</v>
+        <v>1.3415</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.6678</v>
+        <v>1.3415</v>
       </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.6378</v>
+        <v>1.5584</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3603</v>
+        <v>0.3429</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1214</v>
+        <v>0.0823</v>
       </c>
       <c r="E47" t="n">
-        <v>1.6378</v>
+        <v>1.5584</v>
       </c>
       <c r="F47" t="n">
-        <v>2.9302</v>
+        <v>1.6678</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.2924</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3.6884</v>
+        <v>1.6678</v>
       </c>
       <c r="I47" t="n">
-        <v>3.881</v>
+        <v>1.6678</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.2924</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="L47" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.5886</v>
+        <v>1.6678</v>
       </c>
       <c r="N47" t="n">
-        <v>312</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jorko</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.5086</v>
+        <v>1.5476</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3319</v>
+        <v>0.3405</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0625</v>
+        <v>0.0775</v>
       </c>
       <c r="E48" t="n">
-        <v>1.5086</v>
+        <v>1.5476</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5086</v>
+        <v>2.9301</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-1.292</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5086</v>
+        <v>3.6882</v>
       </c>
       <c r="I48" t="n">
-        <v>1.5874</v>
+        <v>3.8808</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-1.292</v>
       </c>
       <c r="K48" t="n">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M48" t="n">
-        <v>1.5874</v>
+        <v>2.5888</v>
       </c>
       <c r="N48" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Jorko</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.4116</v>
+        <v>1.3783</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3106</v>
+        <v>0.3032</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0184</v>
+        <v>0.0018</v>
       </c>
       <c r="E49" t="n">
-        <v>1.4116</v>
+        <v>1.3783</v>
       </c>
       <c r="F49" t="n">
-        <v>2.4906</v>
+        <v>1.5093</v>
       </c>
       <c r="G49" t="n">
-        <v>-1.079</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.7262</v>
+        <v>1.5093</v>
       </c>
       <c r="I49" t="n">
-        <v>2.9424</v>
+        <v>1.5881</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.079</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="L49" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.8634</v>
+        <v>1.5881</v>
       </c>
       <c r="N49" t="n">
-        <v>396</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.3415</v>
+        <v>1.3344</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2951</v>
+        <v>0.2936</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0135</v>
+        <v>-0.0178</v>
       </c>
       <c r="E50" t="n">
-        <v>1.3415</v>
+        <v>1.3344</v>
       </c>
       <c r="F50" t="n">
-        <v>1.3415</v>
+        <v>1.2675</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
       <c r="H50" t="n">
-        <v>1.3415</v>
+        <v>1.2675</v>
       </c>
       <c r="I50" t="n">
-        <v>1.3415</v>
+        <v>1.2675</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
       <c r="K50" t="n">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3415</v>
+        <v>1.3167</v>
       </c>
       <c r="N50" t="n">
-        <v>44</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.3165</v>
+        <v>1.2527</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2896</v>
+        <v>0.2756</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.0249</v>
+        <v>-0.0543</v>
       </c>
       <c r="E51" t="n">
-        <v>1.3165</v>
+        <v>1.2527</v>
       </c>
       <c r="F51" t="n">
-        <v>1.2673</v>
+        <v>2.4919</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0492</v>
+        <v>-1.0794</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2673</v>
+        <v>2.729</v>
       </c>
       <c r="I51" t="n">
-        <v>1.2673</v>
+        <v>2.9455</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0492</v>
+        <v>-1.0794</v>
       </c>
       <c r="K51" t="n">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="L51" t="n">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="M51" t="n">
-        <v>1.3165</v>
+        <v>1.8661</v>
       </c>
       <c r="N51" t="n">
-        <v>266</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.0743</v>
+        <v>1.0405</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2364</v>
+        <v>0.2289</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.1352</v>
+        <v>-0.1491</v>
       </c>
       <c r="E52" t="n">
-        <v>1.0743</v>
+        <v>1.0405</v>
       </c>
       <c r="F52" t="n">
-        <v>1.0743</v>
+        <v>1.0857</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.0743</v>
+        <v>1.0857</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0743</v>
+        <v>1.0857</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1.0743</v>
+        <v>1.0857</v>
       </c>
       <c r="N52" t="n">
         <v>231</v>
@@ -2842,31 +2842,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9271</v>
+        <v>0.837</v>
       </c>
       <c r="C53" t="n">
-        <v>0.204</v>
+        <v>0.1842</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2022</v>
+        <v>-0.24</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9271</v>
+        <v>0.837</v>
       </c>
       <c r="F53" t="n">
-        <v>1.3362</v>
+        <v>1.314</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.4091</v>
+        <v>-0.4092</v>
       </c>
       <c r="H53" t="n">
-        <v>1.3362</v>
+        <v>1.314</v>
       </c>
       <c r="I53" t="n">
-        <v>1.4059</v>
+        <v>1.3826</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.4091</v>
+        <v>-0.4092</v>
       </c>
       <c r="K53" t="n">
         <v>280</v>
@@ -2875,7 +2875,7 @@
         <v>62</v>
       </c>
       <c r="M53" t="n">
-        <v>0.9967999999999999</v>
+        <v>0.9734</v>
       </c>
       <c r="N53" t="n">
         <v>342</v>
@@ -2884,323 +2884,323 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>krazy</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8459</v>
+        <v>0.7932</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1861</v>
+        <v>0.1745</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2391</v>
+        <v>-0.2595</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8459</v>
+        <v>0.7932</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8459</v>
+        <v>0.409</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8459</v>
+        <v>0.409</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8459</v>
+        <v>0.409</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>212</v>
+        <v>44</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8459</v>
+        <v>0.409</v>
       </c>
       <c r="N54" t="n">
-        <v>212</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7398</v>
+        <v>0.7709</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1628</v>
+        <v>0.1696</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2874</v>
+        <v>-0.2695</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7398</v>
+        <v>0.7709</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7398</v>
+        <v>0.7</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7398</v>
+        <v>0.7</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7398</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7398</v>
+        <v>0.7</v>
       </c>
       <c r="N55" t="n">
-        <v>207</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7033</v>
+        <v>0.7484</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1547</v>
+        <v>0.1647</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.304</v>
+        <v>-0.2795</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7033</v>
+        <v>0.7484</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8554</v>
+        <v>0.7389</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1521</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8554</v>
+        <v>0.7389</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9001</v>
+        <v>0.7389</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1521</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="L56" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.748</v>
+        <v>0.7389</v>
       </c>
       <c r="N56" t="n">
-        <v>292</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>krazy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7</v>
+        <v>0.6955</v>
       </c>
       <c r="C57" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3055</v>
+        <v>-0.3032</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7</v>
+        <v>0.6955</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7</v>
+        <v>0.8337</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7</v>
+        <v>0.8337</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.8337</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7</v>
+        <v>0.8337</v>
       </c>
       <c r="N57" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5453</v>
+        <v>0.6204</v>
       </c>
       <c r="C58" t="n">
-        <v>0.12</v>
+        <v>0.1365</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.376</v>
+        <v>-0.3367</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5453</v>
+        <v>0.6204</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5453</v>
+        <v>0.3778</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5453</v>
+        <v>0.3778</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5738</v>
+        <v>0.3778</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>268</v>
+        <v>174</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5738</v>
+        <v>0.3778</v>
       </c>
       <c r="N58" t="n">
-        <v>268</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.409</v>
+        <v>0.5665</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09</v>
+        <v>0.1246</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.438</v>
+        <v>-0.3608</v>
       </c>
       <c r="E59" t="n">
-        <v>0.409</v>
+        <v>0.5665</v>
       </c>
       <c r="F59" t="n">
-        <v>0.409</v>
+        <v>0.8545</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.1521</v>
       </c>
       <c r="H59" t="n">
-        <v>0.409</v>
+        <v>0.8545</v>
       </c>
       <c r="I59" t="n">
-        <v>0.409</v>
+        <v>0.8991</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.1521</v>
       </c>
       <c r="K59" t="n">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M59" t="n">
-        <v>0.409</v>
+        <v>0.747</v>
       </c>
       <c r="N59" t="n">
-        <v>44</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3774</v>
+        <v>0.4382</v>
       </c>
       <c r="C60" t="n">
-        <v>0.083</v>
+        <v>0.0964</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4524</v>
+        <v>-0.4181</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3774</v>
+        <v>0.4382</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3774</v>
+        <v>0.5577</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3774</v>
+        <v>0.5577</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3774</v>
+        <v>0.5868</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3774</v>
+        <v>0.5868</v>
       </c>
       <c r="N60" t="n">
-        <v>174</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0818</v>
+        <v>0.0872</v>
       </c>
       <c r="C61" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.587</v>
+        <v>-0.5749</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0818</v>
+        <v>0.0872</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4351</v>
+        <v>-0.436</v>
       </c>
       <c r="G61" t="n">
         <v>0.5169</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4351</v>
+        <v>-0.436</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4578</v>
+        <v>-0.4588</v>
       </c>
       <c r="J61" t="n">
         <v>0.5169</v>
@@ -3243,7 +3243,7 @@
         <v>73</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05910000000000004</v>
+        <v>0.05810000000000004</v>
       </c>
       <c r="N61" t="n">
         <v>292</v>
@@ -3252,32 +3252,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jeorge</t>
+          <t>snav</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0581</v>
+        <v>-0.1842</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0128</v>
+        <v>-0.0405</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5978</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0581</v>
+        <v>-0.1842</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0581</v>
+        <v>-0.3975</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0581</v>
+        <v>-0.3975</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0581</v>
+        <v>-0.3975</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0581</v>
+        <v>-0.3975</v>
       </c>
       <c r="N62" t="n">
         <v>174</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0244</v>
+        <v>-0.1925</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0054</v>
+        <v>-0.0424</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6131</v>
+        <v>-0.6998</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0244</v>
+        <v>-0.1925</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4399</v>
+        <v>-0.4408</v>
       </c>
       <c r="G63" t="n">
         <v>0.4643</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4399</v>
+        <v>-0.4408</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4629</v>
+        <v>-0.4638</v>
       </c>
       <c r="J63" t="n">
         <v>0.4643</v>
@@ -3335,7 +3335,7 @@
         <v>73</v>
       </c>
       <c r="M63" t="n">
-        <v>0.001400000000000012</v>
+        <v>0.0005000000000000004</v>
       </c>
       <c r="N63" t="n">
         <v>292</v>
@@ -3344,32 +3344,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>nosraC</t>
+          <t>Jeorge</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0051</v>
+        <v>-0.2064</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0011</v>
+        <v>-0.0454</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6219</v>
+        <v>-0.706</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0051</v>
+        <v>-0.2064</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0051</v>
+        <v>0.0583</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0051</v>
+        <v>0.0583</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0051</v>
+        <v>0.0583</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0051</v>
+        <v>0.0583</v>
       </c>
       <c r="N64" t="n">
         <v>174</v>
@@ -3390,32 +3390,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>snav</t>
+          <t>nosraC</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3977</v>
+        <v>-0.2292</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0504</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8052</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3977</v>
+        <v>-0.2292</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3977</v>
+        <v>0.0052</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3977</v>
+        <v>0.0052</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3977</v>
+        <v>0.0052</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3977</v>
+        <v>0.0052</v>
       </c>
       <c r="N65" t="n">
         <v>174</v>
@@ -3436,93 +3436,93 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4213</v>
+        <v>-0.5564</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0927</v>
+        <v>-0.1224</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4213</v>
+        <v>-0.5564</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4213</v>
+        <v>-0.4787</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4213</v>
+        <v>-0.4787</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4213</v>
+        <v>-0.4787</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4213</v>
+        <v>-0.4787</v>
       </c>
       <c r="N66" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4787</v>
+        <v>-0.5865</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1053</v>
+        <v>-0.129</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8421</v>
+        <v>-0.8758</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4787</v>
+        <v>-0.5865</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4787</v>
+        <v>-0.4215</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4787</v>
+        <v>-0.4215</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4787</v>
+        <v>-0.4215</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4787</v>
+        <v>-0.4215</v>
       </c>
       <c r="N67" t="n">
-        <v>44</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68">
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5088</v>
+        <v>-0.6838</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1119</v>
+        <v>-0.1504</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8558</v>
+        <v>-0.9193</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5088</v>
+        <v>-0.6838</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5088</v>
+        <v>-0.5085</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5088</v>
+        <v>-0.5085</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5088</v>
+        <v>-0.5085</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5088</v>
+        <v>-0.5085</v>
       </c>
       <c r="N68" t="n">
         <v>212</v>
@@ -3578,31 +3578,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6202</v>
+        <v>-0.7968</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1365</v>
+        <v>-0.1753</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9065</v>
+        <v>-0.9697</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6202</v>
+        <v>-0.7968</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2638</v>
+        <v>-0.245</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.3564</v>
+        <v>-0.3563</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2638</v>
+        <v>-0.245</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2921</v>
+        <v>-0.2712</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.3564</v>
+        <v>-0.3563</v>
       </c>
       <c r="K69" t="n">
         <v>254</v>
@@ -3611,7 +3611,7 @@
         <v>53</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6485000000000001</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="N69" t="n">
         <v>307</v>
@@ -3620,32 +3620,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>onic</t>
+          <t>zeRRoFIX</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6264</v>
+        <v>-0.7991</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1378</v>
+        <v>-0.1758</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9094</v>
+        <v>-0.9708</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6264</v>
+        <v>-0.7991</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6264</v>
+        <v>-0.6166</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6264</v>
+        <v>-0.6166</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6264</v>
+        <v>-0.6166</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6264</v>
+        <v>-0.6166</v>
       </c>
       <c r="N70" t="n">
         <v>207</v>
@@ -3666,170 +3666,170 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>zeRRoFIX</t>
+          <t>mhL</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6412</v>
+        <v>-0.8012</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1411</v>
+        <v>-0.1763</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9161</v>
+        <v>-0.9717</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6412</v>
+        <v>-0.8012</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6412</v>
+        <v>-0.6925</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6412</v>
+        <v>-0.6925</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6412</v>
+        <v>-0.6925</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6412</v>
+        <v>-0.6925</v>
       </c>
       <c r="N71" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mhL</t>
+          <t>aragornN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6916</v>
+        <v>-0.8425</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.1522</v>
+        <v>-0.1854</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.9901</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6916</v>
+        <v>-0.8425</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6916</v>
+        <v>-0.7831</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6916</v>
+        <v>-0.7831</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6916</v>
+        <v>-0.7831</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6916</v>
+        <v>-0.7831</v>
       </c>
       <c r="N72" t="n">
-        <v>231</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>aragornN</t>
+          <t>cptkurtka023</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7834</v>
+        <v>-0.8768</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.1724</v>
+        <v>-0.1929</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9808</v>
+        <v>-1.0055</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7834</v>
+        <v>-0.8768</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7834</v>
+        <v>-0.8619</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7834</v>
+        <v>-0.8619</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7834</v>
+        <v>-0.8619</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7834</v>
+        <v>-0.8619</v>
       </c>
       <c r="N73" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cptkurtka023</t>
+          <t>onic</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8611</v>
+        <v>-1.0002</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1895</v>
+        <v>-0.2201</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0162</v>
+        <v>-1.0606</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8611</v>
+        <v>-1.0002</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.8611</v>
+        <v>-0.6273</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.8611</v>
+        <v>-0.6273</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.8611</v>
+        <v>-0.6273</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.8611</v>
+        <v>-0.6273</v>
       </c>
       <c r="N74" t="n">
         <v>207</v>
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9656</v>
+        <v>-1.6975</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2124</v>
+        <v>-0.3735</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0638</v>
+        <v>-1.3721</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9656</v>
+        <v>-1.6975</v>
       </c>
       <c r="F75" t="n">
         <v>-0.9656</v>
@@ -3896,93 +3896,93 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.5184</v>
+        <v>-1.7945</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.3341</v>
+        <v>-0.3948</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3154</v>
+        <v>-1.4154</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.5184</v>
+        <v>-1.7945</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3076</v>
+        <v>-1.6496</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.2108</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3076</v>
+        <v>-1.6496</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3759</v>
+        <v>-1.6496</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.2108</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L76" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.5867</v>
+        <v>-1.6496</v>
       </c>
       <c r="N76" t="n">
-        <v>345</v>
+        <v>151</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.661</v>
+        <v>-1.8404</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3654</v>
+        <v>-0.4049</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3803</v>
+        <v>-1.4359</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.661</v>
+        <v>-1.8404</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.661</v>
+        <v>-1.3343</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-0.1978</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.661</v>
+        <v>-1.3343</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.661</v>
+        <v>-1.404</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>-0.1978</v>
       </c>
       <c r="K77" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.661</v>
+        <v>-1.6018</v>
       </c>
       <c r="N77" t="n">
-        <v>151</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78">
@@ -3992,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.007</v>
+        <v>-2.3802</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.4416</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5378</v>
+        <v>-1.677</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.007</v>
+        <v>-2.3802</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.9433</v>
+        <v>-1.9408</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0523</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.9433</v>
+        <v>-1.9408</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.0447</v>
+        <v>-2.0421</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0523</v>
       </c>
       <c r="K78" t="n">
         <v>280</v>
@@ -4025,7 +4025,7 @@
         <v>62</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.1084</v>
+        <v>-2.0944</v>
       </c>
       <c r="N78" t="n">
         <v>342</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.2148</v>
+        <v>-2.4687</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4873</v>
+        <v>-0.5431</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6324</v>
+        <v>-1.7165</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.2148</v>
+        <v>-2.4687</v>
       </c>
       <c r="F79" t="n">
         <v>-2.2148</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.0317</v>
+        <v>-3.2567</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.667</v>
+        <v>-0.7165</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.0043</v>
+        <v>-2.0685</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.0317</v>
+        <v>-3.2567</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.0373</v>
+        <v>-2.0468</v>
       </c>
       <c r="G80" t="n">
         <v>-0.9944</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.0373</v>
+        <v>-2.0468</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.0373</v>
+        <v>-2.0468</v>
       </c>
       <c r="J80" t="n">
         <v>-0.9944</v>
@@ -4117,7 +4117,7 @@
         <v>66</v>
       </c>
       <c r="M80" t="n">
-        <v>-3.0317</v>
+        <v>-3.0412</v>
       </c>
       <c r="N80" t="n">
         <v>266</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.554</v>
+        <v>-3.9426</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.7819</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2421</v>
+        <v>-2.3749</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.554</v>
+        <v>-3.9426</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.554</v>
+        <v>-3.5458</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.554</v>
+        <v>-3.5458</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.554</v>
+        <v>-3.5458</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.554</v>
+        <v>-3.5458</v>
       </c>
       <c r="N81" t="n">
         <v>231</v>
@@ -4869,10 +4869,10 @@
         <v>1.84</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6372</v>
+        <v>1.6376</v>
       </c>
       <c r="J17" t="n">
-        <v>29.4696</v>
+        <v>29.4768</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.44</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9876</v>
+        <v>0.9878</v>
       </c>
       <c r="J18" t="n">
-        <v>17.7768</v>
+        <v>17.7804</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.37</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8615</v>
+        <v>0.8617</v>
       </c>
       <c r="J19" t="n">
-        <v>15.507</v>
+        <v>15.5106</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>1.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7265</v>
+        <v>0.7268</v>
       </c>
       <c r="J20" t="n">
-        <v>13.077</v>
+        <v>13.0824</v>
       </c>
     </row>
     <row r="21">
@@ -5026,13 +5026,13 @@
         <v>18</v>
       </c>
       <c r="H21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2235</v>
+        <v>0.1957</v>
       </c>
       <c r="J21" t="n">
-        <v>4.023</v>
+        <v>3.5226</v>
       </c>
     </row>
     <row r="22">
@@ -5709,10 +5709,10 @@
         <v>1.42</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9443</v>
+        <v>0.9445</v>
       </c>
       <c r="J38" t="n">
-        <v>15.1088</v>
+        <v>15.112</v>
       </c>
     </row>
     <row r="39">
@@ -5746,13 +5746,13 @@
         <v>16</v>
       </c>
       <c r="H39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9076</v>
+        <v>0.8893</v>
       </c>
       <c r="J39" t="n">
-        <v>14.5216</v>
+        <v>14.2288</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.19</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4824</v>
+        <v>0.4827</v>
       </c>
       <c r="J40" t="n">
-        <v>7.7184</v>
+        <v>7.7232</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5251</v>
+        <v>-0.5248</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.4016</v>
+        <v>-8.396800000000001</v>
       </c>
     </row>
     <row r="42">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0029</v>
+        <v>-0.0042</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.0435</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="53">
@@ -6306,13 +6306,13 @@
         <v>15</v>
       </c>
       <c r="H53" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.171</v>
+        <v>-0.1607</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.565</v>
+        <v>-2.4105</v>
       </c>
     </row>
     <row r="54">
@@ -6346,13 +6346,13 @@
         <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3132</v>
+        <v>-0.3045</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.698</v>
+        <v>-4.5675</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.47</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5148</v>
+        <v>-0.5154</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.722</v>
+        <v>-7.731</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.31</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6543</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.814500000000001</v>
+        <v>-9.820499999999999</v>
       </c>
     </row>
     <row r="57">
@@ -7869,10 +7869,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4801</v>
+        <v>0.4797</v>
       </c>
       <c r="J92" t="n">
-        <v>11.0423</v>
+        <v>11.0331</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>0.98</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0406</v>
+        <v>-0.0408</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.9338</v>
+        <v>-0.9384</v>
       </c>
     </row>
     <row r="94">
@@ -7946,13 +7946,13 @@
         <v>23</v>
       </c>
       <c r="H94" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1658</v>
+        <v>-0.1549</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.8134</v>
+        <v>-3.5627</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1766</v>
+        <v>-0.1768</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.0618</v>
+        <v>-4.0664</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2083</v>
+        <v>-0.2084</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.7909</v>
+        <v>-4.7932</v>
       </c>
     </row>
     <row r="97">
@@ -8066,13 +8066,13 @@
         <v>23</v>
       </c>
       <c r="H97" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2404</v>
+        <v>1.2534</v>
       </c>
       <c r="J97" t="n">
-        <v>28.5292</v>
+        <v>28.8282</v>
       </c>
     </row>
     <row r="98">
@@ -8186,13 +8186,13 @@
         <v>23</v>
       </c>
       <c r="H100" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4556</v>
+        <v>-0.4806</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.4788</v>
+        <v>-11.0538</v>
       </c>
     </row>
     <row r="101">
@@ -9066,13 +9066,13 @@
         <v>22</v>
       </c>
       <c r="H122" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8979</v>
+        <v>0.8841</v>
       </c>
       <c r="J122" t="n">
-        <v>19.7538</v>
+        <v>19.4502</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8264</v>
+        <v>0.8268</v>
       </c>
       <c r="J123" t="n">
-        <v>18.1808</v>
+        <v>18.1896</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3682</v>
+        <v>0.3685</v>
       </c>
       <c r="J124" t="n">
-        <v>8.1004</v>
+        <v>8.106999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2645</v>
+        <v>0.2649</v>
       </c>
       <c r="J125" t="n">
-        <v>5.819</v>
+        <v>5.8278</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8156</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.952</v>
+        <v>-17.9432</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4437</v>
+        <v>0.4433</v>
       </c>
       <c r="J127" t="n">
-        <v>9.7614</v>
+        <v>9.752599999999999</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.13</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3073</v>
+        <v>0.3069</v>
       </c>
       <c r="J128" t="n">
-        <v>6.7606</v>
+        <v>6.7518</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1</v>
+        <v>-0.1001</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.2</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="130">
@@ -9386,13 +9386,13 @@
         <v>22</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.148</v>
+        <v>-0.1366</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.256</v>
+        <v>-3.0052</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.88</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1704</v>
+        <v>-0.1705</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.7488</v>
+        <v>-3.751</v>
       </c>
     </row>
     <row r="132">
@@ -9669,10 +9669,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9212</v>
+        <v>0.9218</v>
       </c>
       <c r="J137" t="n">
-        <v>22.1088</v>
+        <v>22.1232</v>
       </c>
     </row>
     <row r="138">
@@ -9706,13 +9706,13 @@
         <v>24</v>
       </c>
       <c r="H138" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.039</v>
+        <v>-0.0027</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9360000000000001</v>
+        <v>-0.0648</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1155</v>
+        <v>-0.1153</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.772</v>
+        <v>-2.7672</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.91</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1395</v>
+        <v>-0.1393</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.348</v>
+        <v>-3.3432</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3146</v>
+        <v>-0.3144</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.5504</v>
+        <v>-7.5456</v>
       </c>
     </row>
     <row r="142">
@@ -10069,10 +10069,10 @@
         <v>1.65</v>
       </c>
       <c r="I147" t="n">
-        <v>0.956</v>
+        <v>0.9552</v>
       </c>
       <c r="J147" t="n">
-        <v>27.724</v>
+        <v>27.7008</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1806</v>
+        <v>0.1802</v>
       </c>
       <c r="J148" t="n">
-        <v>5.2374</v>
+        <v>5.2258</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2169</v>
+        <v>-0.217</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.2901</v>
+        <v>-6.293</v>
       </c>
     </row>
     <row r="150">
@@ -10186,13 +10186,13 @@
         <v>29</v>
       </c>
       <c r="H150" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3607</v>
+        <v>-0.3517</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.4603</v>
+        <v>-10.1993</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.527</v>
+        <v>-0.5272</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.283</v>
+        <v>-15.2888</v>
       </c>
     </row>
     <row r="152">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3637</v>
+        <v>0.3632</v>
       </c>
       <c r="J187" t="n">
-        <v>8.0014</v>
+        <v>7.9904</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.206</v>
+        <v>0.2057</v>
       </c>
       <c r="J188" t="n">
-        <v>4.532</v>
+        <v>4.5254</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0221</v>
+        <v>-0.0222</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.4862</v>
+        <v>-0.4884</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.86</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1862</v>
+        <v>-0.1864</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.0964</v>
+        <v>-4.1008</v>
       </c>
     </row>
     <row r="191">
@@ -11826,13 +11826,13 @@
         <v>22</v>
       </c>
       <c r="H191" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4503</v>
+        <v>-0.4417</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.906599999999999</v>
+        <v>-9.7174</v>
       </c>
     </row>
     <row r="192">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5678</v>
+        <v>0.5673</v>
       </c>
       <c r="J212" t="n">
-        <v>30.6612</v>
+        <v>30.6342</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5451</v>
+        <v>0.5446</v>
       </c>
       <c r="J213" t="n">
-        <v>29.4354</v>
+        <v>29.4084</v>
       </c>
     </row>
     <row r="214">
@@ -12746,13 +12746,13 @@
         <v>54</v>
       </c>
       <c r="H214" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4517</v>
+        <v>0.475</v>
       </c>
       <c r="J214" t="n">
-        <v>24.3918</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1596</v>
+        <v>0.1593</v>
       </c>
       <c r="J215" t="n">
-        <v>8.618399999999999</v>
+        <v>8.6022</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6703</v>
       </c>
       <c r="J216" t="n">
-        <v>-36.1746</v>
+        <v>-36.1962</v>
       </c>
     </row>
     <row r="217">
@@ -13869,10 +13869,10 @@
         <v>1.59</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1922</v>
+        <v>1.1925</v>
       </c>
       <c r="J242" t="n">
-        <v>20.2674</v>
+        <v>20.2725</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.58</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1793</v>
+        <v>1.1796</v>
       </c>
       <c r="J243" t="n">
-        <v>20.0481</v>
+        <v>20.0532</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.3</v>
       </c>
       <c r="I244" t="n">
-        <v>0.731</v>
+        <v>0.7313</v>
       </c>
       <c r="J244" t="n">
-        <v>12.427</v>
+        <v>12.4321</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.25</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6293</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>10.6981</v>
+        <v>10.7015</v>
       </c>
     </row>
     <row r="246">
@@ -14026,13 +14026,13 @@
         <v>17</v>
       </c>
       <c r="H246" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I246" t="n">
-        <v>0.3831</v>
+        <v>0.359</v>
       </c>
       <c r="J246" t="n">
-        <v>6.5127</v>
+        <v>6.103</v>
       </c>
     </row>
     <row r="247">
@@ -15069,10 +15069,10 @@
         <v>1.35</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6924</v>
+        <v>0.6931</v>
       </c>
       <c r="J272" t="n">
-        <v>15.2328</v>
+        <v>15.2482</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.29</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5972</v>
+        <v>0.5979</v>
       </c>
       <c r="J273" t="n">
-        <v>13.1384</v>
+        <v>13.1538</v>
       </c>
     </row>
     <row r="274">
@@ -15146,13 +15146,13 @@
         <v>22</v>
       </c>
       <c r="H274" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1312</v>
+        <v>-0.1424</v>
       </c>
       <c r="J274" t="n">
-        <v>-2.8864</v>
+        <v>-3.1328</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.424</v>
+        <v>-0.4238</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.327999999999999</v>
+        <v>-9.323600000000001</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.58</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4503</v>
+        <v>-0.4501</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.906599999999999</v>
+        <v>-9.902200000000001</v>
       </c>
     </row>
     <row r="277">
@@ -15866,13 +15866,13 @@
         <v>22</v>
       </c>
       <c r="H292" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6293</v>
+        <v>0.614</v>
       </c>
       <c r="J292" t="n">
-        <v>13.8446</v>
+        <v>13.508</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.99</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0221</v>
+        <v>-0.0219</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.4862</v>
+        <v>-0.4818</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.9</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1426</v>
+        <v>-0.1424</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.1372</v>
+        <v>-3.1328</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1648</v>
+        <v>-0.1646</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.6256</v>
+        <v>-3.6212</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.66</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3794</v>
+        <v>-0.3792</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.3468</v>
+        <v>-8.3424</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.52</v>
       </c>
       <c r="I297" t="n">
-        <v>1.124</v>
+        <v>1.1236</v>
       </c>
       <c r="J297" t="n">
-        <v>24.728</v>
+        <v>24.7192</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.43</v>
       </c>
       <c r="I298" t="n">
-        <v>0.9932</v>
+        <v>0.9928</v>
       </c>
       <c r="J298" t="n">
-        <v>21.8504</v>
+        <v>21.8416</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.34</v>
       </c>
       <c r="I299" t="n">
-        <v>0.8258</v>
+        <v>0.8254</v>
       </c>
       <c r="J299" t="n">
-        <v>18.1676</v>
+        <v>18.1588</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.12</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3555</v>
+        <v>0.3551</v>
       </c>
       <c r="J300" t="n">
-        <v>7.821</v>
+        <v>7.8122</v>
       </c>
     </row>
     <row r="301">
@@ -16226,13 +16226,13 @@
         <v>22</v>
       </c>
       <c r="H301" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.699</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.378</v>
+        <v>-14.8918</v>
       </c>
     </row>
     <row r="302">
@@ -17669,10 +17669,10 @@
         <v>1.07</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2176</v>
+        <v>0.217</v>
       </c>
       <c r="J337" t="n">
-        <v>4.5696</v>
+        <v>4.557</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.03</v>
       </c>
       <c r="I338" t="n">
-        <v>0.1226</v>
+        <v>0.1221</v>
       </c>
       <c r="J338" t="n">
-        <v>2.5746</v>
+        <v>2.5641</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.96</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0634</v>
+        <v>-0.0636</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.3314</v>
+        <v>-1.3356</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.86</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1805</v>
+        <v>-0.1807</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.7905</v>
+        <v>-3.7947</v>
       </c>
     </row>
     <row r="341">
@@ -17826,13 +17826,13 @@
         <v>21</v>
       </c>
       <c r="H341" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5304</v>
+        <v>-0.522</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.1384</v>
+        <v>-10.962</v>
       </c>
     </row>
     <row r="342">
@@ -20469,10 +20469,10 @@
         <v>1.49</v>
       </c>
       <c r="I407" t="n">
-        <v>0.6237</v>
+        <v>0.6241</v>
       </c>
       <c r="J407" t="n">
-        <v>14.3451</v>
+        <v>14.3543</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.32</v>
       </c>
       <c r="I408" t="n">
-        <v>0.4416</v>
+        <v>0.4418</v>
       </c>
       <c r="J408" t="n">
-        <v>10.1568</v>
+        <v>10.1614</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.11</v>
       </c>
       <c r="I409" t="n">
-        <v>0.1887</v>
+        <v>0.1888</v>
       </c>
       <c r="J409" t="n">
-        <v>4.3401</v>
+        <v>4.3424</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>1.08</v>
       </c>
       <c r="I410" t="n">
-        <v>0.1455</v>
+        <v>0.1457</v>
       </c>
       <c r="J410" t="n">
-        <v>3.3465</v>
+        <v>3.3511</v>
       </c>
     </row>
     <row r="411">
@@ -20626,13 +20626,13 @@
         <v>23</v>
       </c>
       <c r="H411" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3225</v>
+        <v>-0.3317</v>
       </c>
       <c r="J411" t="n">
-        <v>-7.4175</v>
+        <v>-7.6291</v>
       </c>
     </row>
     <row r="412">
@@ -21066,13 +21066,13 @@
         <v>17</v>
       </c>
       <c r="H422" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I422" t="n">
-        <v>1.2852</v>
+        <v>1.273</v>
       </c>
       <c r="J422" t="n">
-        <v>21.8484</v>
+        <v>21.641</v>
       </c>
     </row>
     <row r="423">
@@ -21109,10 +21109,10 @@
         <v>1.6</v>
       </c>
       <c r="I423" t="n">
-        <v>1.1971</v>
+        <v>1.1974</v>
       </c>
       <c r="J423" t="n">
-        <v>20.3507</v>
+        <v>20.3558</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>1.46</v>
       </c>
       <c r="I424" t="n">
-        <v>1.0122</v>
+        <v>1.0123</v>
       </c>
       <c r="J424" t="n">
-        <v>17.2074</v>
+        <v>17.2091</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>1.24</v>
       </c>
       <c r="I425" t="n">
-        <v>0.6004</v>
+        <v>0.6007</v>
       </c>
       <c r="J425" t="n">
-        <v>10.2068</v>
+        <v>10.2119</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>1.16</v>
       </c>
       <c r="I426" t="n">
-        <v>0.4226</v>
+        <v>0.4229</v>
       </c>
       <c r="J426" t="n">
-        <v>7.1842</v>
+        <v>7.1893</v>
       </c>
     </row>
     <row r="427">
@@ -21506,13 +21506,13 @@
         <v>24</v>
       </c>
       <c r="H433" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I433" t="n">
-        <v>0.3704</v>
+        <v>0.3883</v>
       </c>
       <c r="J433" t="n">
-        <v>8.8896</v>
+        <v>9.3192</v>
       </c>
     </row>
     <row r="434">
@@ -21546,13 +21546,13 @@
         <v>24</v>
       </c>
       <c r="H434" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I434" t="n">
-        <v>0.1748</v>
+        <v>0.1523</v>
       </c>
       <c r="J434" t="n">
-        <v>4.1952</v>
+        <v>3.6552</v>
       </c>
     </row>
     <row r="435">
@@ -22066,7 +22066,7 @@
         <v>19</v>
       </c>
       <c r="H447" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="I447" t="n">
         <v>1.9372</v>
@@ -22106,13 +22106,13 @@
         <v>19</v>
       </c>
       <c r="H448" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I448" t="n">
-        <v>0.9035</v>
+        <v>0.922</v>
       </c>
       <c r="J448" t="n">
-        <v>17.1665</v>
+        <v>17.518</v>
       </c>
     </row>
     <row r="449">
@@ -22146,13 +22146,13 @@
         <v>19</v>
       </c>
       <c r="H449" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I449" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.6944</v>
       </c>
       <c r="J449" t="n">
-        <v>13.5698</v>
+        <v>13.1936</v>
       </c>
     </row>
     <row r="450">
@@ -22189,10 +22189,10 @@
         <v>1.05</v>
       </c>
       <c r="I450" t="n">
-        <v>0.145</v>
+        <v>0.1453</v>
       </c>
       <c r="J450" t="n">
-        <v>2.755</v>
+        <v>2.7607</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.76</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="J451" t="n">
-        <v>-14.0106</v>
+        <v>-14.0049</v>
       </c>
     </row>
     <row r="452">
@@ -22386,13 +22386,13 @@
         <v>17</v>
       </c>
       <c r="H455" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I455" t="n">
-        <v>0.3909</v>
+        <v>0.4149</v>
       </c>
       <c r="J455" t="n">
-        <v>6.6453</v>
+        <v>7.0533</v>
       </c>
     </row>
     <row r="456">
@@ -22426,13 +22426,13 @@
         <v>17</v>
       </c>
       <c r="H456" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I456" t="n">
-        <v>0.2366</v>
+        <v>0.2085</v>
       </c>
       <c r="J456" t="n">
-        <v>4.0222</v>
+        <v>3.5445</v>
       </c>
     </row>
     <row r="457">
@@ -22469,10 +22469,10 @@
         <v>1.08</v>
       </c>
       <c r="I457" t="n">
-        <v>0.2494</v>
+        <v>0.2487</v>
       </c>
       <c r="J457" t="n">
-        <v>4.2398</v>
+        <v>4.2279</v>
       </c>
     </row>
     <row r="458">
@@ -22509,10 +22509,10 @@
         <v>1.05</v>
       </c>
       <c r="I458" t="n">
-        <v>0.1818</v>
+        <v>0.1812</v>
       </c>
       <c r="J458" t="n">
-        <v>3.0906</v>
+        <v>3.0804</v>
       </c>
     </row>
     <row r="459">
@@ -22549,10 +22549,10 @@
         <v>0.83</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.2084</v>
+        <v>-0.2085</v>
       </c>
       <c r="J459" t="n">
-        <v>-3.5428</v>
+        <v>-3.5445</v>
       </c>
     </row>
     <row r="460">
@@ -22589,10 +22589,10 @@
         <v>0.64</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.3872</v>
+        <v>-0.3874</v>
       </c>
       <c r="J460" t="n">
-        <v>-6.5824</v>
+        <v>-6.5858</v>
       </c>
     </row>
     <row r="461">
@@ -22626,13 +22626,13 @@
         <v>17</v>
       </c>
       <c r="H461" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.3962</v>
+        <v>-0.3874</v>
       </c>
       <c r="J461" t="n">
-        <v>-6.7354</v>
+        <v>-6.5858</v>
       </c>
     </row>
     <row r="462">
@@ -23066,13 +23066,13 @@
         <v>22</v>
       </c>
       <c r="H472" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I472" t="n">
-        <v>1.3547</v>
+        <v>1.3793</v>
       </c>
       <c r="J472" t="n">
-        <v>29.8034</v>
+        <v>30.3446</v>
       </c>
     </row>
     <row r="473">
@@ -23109,10 +23109,10 @@
         <v>1.47</v>
       </c>
       <c r="I473" t="n">
-        <v>1.0497</v>
+        <v>1.049</v>
       </c>
       <c r="J473" t="n">
-        <v>23.0934</v>
+        <v>23.078</v>
       </c>
     </row>
     <row r="474">
@@ -23149,10 +23149,10 @@
         <v>1.2</v>
       </c>
       <c r="I474" t="n">
-        <v>0.5377</v>
+        <v>0.5372</v>
       </c>
       <c r="J474" t="n">
-        <v>11.8294</v>
+        <v>11.8184</v>
       </c>
     </row>
     <row r="475">
@@ -23189,10 +23189,10 @@
         <v>1.06</v>
       </c>
       <c r="I475" t="n">
-        <v>0.1889</v>
+        <v>0.1882</v>
       </c>
       <c r="J475" t="n">
-        <v>4.1558</v>
+        <v>4.1404</v>
       </c>
     </row>
     <row r="476">
@@ -23229,10 +23229,10 @@
         <v>0.89</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.4173</v>
+        <v>-0.4179</v>
       </c>
       <c r="J476" t="n">
-        <v>-9.1806</v>
+        <v>-9.1938</v>
       </c>
     </row>
     <row r="477">
@@ -26866,13 +26866,13 @@
         <v>20</v>
       </c>
       <c r="H567" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I567" t="n">
-        <v>1.5895</v>
+        <v>1.6011</v>
       </c>
       <c r="J567" t="n">
-        <v>31.79</v>
+        <v>32.022</v>
       </c>
     </row>
     <row r="568">
@@ -26909,10 +26909,10 @@
         <v>1.62</v>
       </c>
       <c r="I568" t="n">
-        <v>1.2391</v>
+        <v>1.2387</v>
       </c>
       <c r="J568" t="n">
-        <v>24.782</v>
+        <v>24.774</v>
       </c>
     </row>
     <row r="569">
@@ -26949,10 +26949,10 @@
         <v>1.31</v>
       </c>
       <c r="I569" t="n">
-        <v>0.7562</v>
+        <v>0.756</v>
       </c>
       <c r="J569" t="n">
-        <v>15.124</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>1.02</v>
       </c>
       <c r="I570" t="n">
-        <v>0.0469</v>
+        <v>0.0465</v>
       </c>
       <c r="J570" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.77</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.7121</v>
+        <v>-0.7123</v>
       </c>
       <c r="J571" t="n">
-        <v>-14.242</v>
+        <v>-14.246</v>
       </c>
     </row>
     <row r="572">
@@ -28269,10 +28269,10 @@
         <v>1.22</v>
       </c>
       <c r="I602" t="n">
-        <v>0.3643</v>
+        <v>0.3636</v>
       </c>
       <c r="J602" t="n">
-        <v>8.7432</v>
+        <v>8.7264</v>
       </c>
     </row>
     <row r="603">
@@ -28306,13 +28306,13 @@
         <v>24</v>
       </c>
       <c r="H603" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I603" t="n">
-        <v>0.311</v>
+        <v>0.3238</v>
       </c>
       <c r="J603" t="n">
-        <v>7.464</v>
+        <v>7.7712</v>
       </c>
     </row>
     <row r="604">
@@ -28349,10 +28349,10 @@
         <v>0.99</v>
       </c>
       <c r="I604" t="n">
-        <v>-0.0258</v>
+        <v>-0.026</v>
       </c>
       <c r="J604" t="n">
-        <v>-0.6192</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="605">
@@ -28386,13 +28386,13 @@
         <v>24</v>
       </c>
       <c r="H605" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I605" t="n">
-        <v>-0.1245</v>
+        <v>-0.1127</v>
       </c>
       <c r="J605" t="n">
-        <v>-2.988</v>
+        <v>-2.7048</v>
       </c>
     </row>
     <row r="606">
@@ -28429,10 +28429,10 @@
         <v>0.74</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.3113</v>
+        <v>-0.3117</v>
       </c>
       <c r="J606" t="n">
-        <v>-7.4712</v>
+        <v>-7.4808</v>
       </c>
     </row>
     <row r="607">
@@ -28666,13 +28666,13 @@
         <v>17</v>
       </c>
       <c r="H612" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="I612" t="n">
-        <v>1.9372</v>
+        <v>1.9293</v>
       </c>
       <c r="J612" t="n">
-        <v>32.9324</v>
+        <v>32.7981</v>
       </c>
     </row>
     <row r="613">
@@ -28709,10 +28709,10 @@
         <v>1.43</v>
       </c>
       <c r="I613" t="n">
-        <v>0.9658</v>
+        <v>0.9659</v>
       </c>
       <c r="J613" t="n">
-        <v>16.4186</v>
+        <v>16.4203</v>
       </c>
     </row>
     <row r="614">
@@ -28749,10 +28749,10 @@
         <v>1.4</v>
       </c>
       <c r="I614" t="n">
-        <v>0.915</v>
+        <v>0.9152</v>
       </c>
       <c r="J614" t="n">
-        <v>15.555</v>
+        <v>15.5584</v>
       </c>
     </row>
     <row r="615">
@@ -28789,10 +28789,10 @@
         <v>1.25</v>
       </c>
       <c r="I615" t="n">
-        <v>0.6224</v>
+        <v>0.6226</v>
       </c>
       <c r="J615" t="n">
-        <v>10.5808</v>
+        <v>10.5842</v>
       </c>
     </row>
     <row r="616">
@@ -28829,10 +28829,10 @@
         <v>0.8</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.6577</v>
+        <v>-0.6574</v>
       </c>
       <c r="J616" t="n">
-        <v>-11.1809</v>
+        <v>-11.1758</v>
       </c>
     </row>
     <row r="617">
@@ -29269,10 +29269,10 @@
         <v>1.44</v>
       </c>
       <c r="I627" t="n">
-        <v>0.8703</v>
+        <v>0.8693</v>
       </c>
       <c r="J627" t="n">
-        <v>19.1466</v>
+        <v>19.1246</v>
       </c>
     </row>
     <row r="628">
@@ -29309,10 +29309,10 @@
         <v>0.9</v>
       </c>
       <c r="I628" t="n">
-        <v>-0.1364</v>
+        <v>-0.1366</v>
       </c>
       <c r="J628" t="n">
-        <v>-3.0008</v>
+        <v>-3.0052</v>
       </c>
     </row>
     <row r="629">
@@ -29349,10 +29349,10 @@
         <v>0.8</v>
       </c>
       <c r="I629" t="n">
-        <v>-0.2391</v>
+        <v>-0.2393</v>
       </c>
       <c r="J629" t="n">
-        <v>-5.2602</v>
+        <v>-5.2646</v>
       </c>
     </row>
     <row r="630">
@@ -29389,10 +29389,10 @@
         <v>0.71</v>
       </c>
       <c r="I630" t="n">
-        <v>-0.3248</v>
+        <v>-0.325</v>
       </c>
       <c r="J630" t="n">
-        <v>-7.1456</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="631">
@@ -29426,13 +29426,13 @@
         <v>22</v>
       </c>
       <c r="H631" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.5541</v>
+        <v>-0.5458</v>
       </c>
       <c r="J631" t="n">
-        <v>-12.1902</v>
+        <v>-12.0076</v>
       </c>
     </row>
     <row r="632">
@@ -29669,10 +29669,10 @@
         <v>1.33</v>
       </c>
       <c r="I637" t="n">
-        <v>0.6576</v>
+        <v>0.6583</v>
       </c>
       <c r="J637" t="n">
-        <v>13.152</v>
+        <v>13.166</v>
       </c>
     </row>
     <row r="638">
@@ -29709,10 +29709,10 @@
         <v>1.27</v>
       </c>
       <c r="I638" t="n">
-        <v>0.5616</v>
+        <v>0.5622</v>
       </c>
       <c r="J638" t="n">
-        <v>11.232</v>
+        <v>11.244</v>
       </c>
     </row>
     <row r="639">
@@ -29749,10 +29749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I639" t="n">
-        <v>-0.0959</v>
+        <v>-0.0958</v>
       </c>
       <c r="J639" t="n">
-        <v>-1.918</v>
+        <v>-1.916</v>
       </c>
     </row>
     <row r="640">
@@ -29786,13 +29786,13 @@
         <v>20</v>
       </c>
       <c r="H640" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I640" t="n">
-        <v>-0.2682</v>
+        <v>-0.2777</v>
       </c>
       <c r="J640" t="n">
-        <v>-5.364</v>
+        <v>-5.554</v>
       </c>
     </row>
     <row r="641">
@@ -29829,10 +29829,10 @@
         <v>0.47</v>
       </c>
       <c r="I641" t="n">
-        <v>-0.5451</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J641" t="n">
-        <v>-10.902</v>
+        <v>-10.898</v>
       </c>
     </row>
     <row r="642">
@@ -30669,10 +30669,10 @@
         <v>1.42</v>
       </c>
       <c r="I662" t="n">
-        <v>0.9969</v>
+        <v>0.9963</v>
       </c>
       <c r="J662" t="n">
-        <v>29.907</v>
+        <v>29.889</v>
       </c>
     </row>
     <row r="663">
@@ -30706,13 +30706,13 @@
         <v>30</v>
       </c>
       <c r="H663" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I663" t="n">
-        <v>0.9244</v>
+        <v>0.9429</v>
       </c>
       <c r="J663" t="n">
-        <v>27.732</v>
+        <v>28.287</v>
       </c>
     </row>
     <row r="664">
@@ -30749,10 +30749,10 @@
         <v>1.08</v>
       </c>
       <c r="I664" t="n">
-        <v>0.2652</v>
+        <v>0.2649</v>
       </c>
       <c r="J664" t="n">
-        <v>7.956</v>
+        <v>7.947</v>
       </c>
     </row>
     <row r="665">
@@ -30789,10 +30789,10 @@
         <v>1</v>
       </c>
       <c r="I665" t="n">
-        <v>-0.0243</v>
+        <v>-0.0247</v>
       </c>
       <c r="J665" t="n">
-        <v>-0.729</v>
+        <v>-0.741</v>
       </c>
     </row>
     <row r="666">
@@ -30829,10 +30829,10 @@
         <v>0.86</v>
       </c>
       <c r="I666" t="n">
-        <v>-0.4734</v>
+        <v>-0.4738</v>
       </c>
       <c r="J666" t="n">
-        <v>-14.202</v>
+        <v>-14.214</v>
       </c>
     </row>
     <row r="667">
@@ -31266,13 +31266,13 @@
         <v>24</v>
       </c>
       <c r="H677" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I677" t="n">
-        <v>1.3925</v>
+        <v>1.4049</v>
       </c>
       <c r="J677" t="n">
-        <v>33.42</v>
+        <v>33.7176</v>
       </c>
     </row>
     <row r="678">
@@ -31309,10 +31309,10 @@
         <v>1.31</v>
       </c>
       <c r="I678" t="n">
-        <v>0.779</v>
+        <v>0.7785</v>
       </c>
       <c r="J678" t="n">
-        <v>18.696</v>
+        <v>18.684</v>
       </c>
     </row>
     <row r="679">
@@ -31349,10 +31349,10 @@
         <v>0.98</v>
       </c>
       <c r="I679" t="n">
-        <v>-0.1299</v>
+        <v>-0.1302</v>
       </c>
       <c r="J679" t="n">
-        <v>-3.1176</v>
+        <v>-3.1248</v>
       </c>
     </row>
     <row r="680">
@@ -31389,10 +31389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I680" t="n">
-        <v>-0.2628</v>
+        <v>-0.2631</v>
       </c>
       <c r="J680" t="n">
-        <v>-6.3072</v>
+        <v>-6.3144</v>
       </c>
     </row>
     <row r="681">
@@ -31429,10 +31429,10 @@
         <v>0.92</v>
       </c>
       <c r="I681" t="n">
-        <v>-0.3205</v>
+        <v>-0.3209</v>
       </c>
       <c r="J681" t="n">
-        <v>-7.692</v>
+        <v>-7.7016</v>
       </c>
     </row>
     <row r="682">
@@ -31669,10 +31669,10 @@
         <v>1.19</v>
       </c>
       <c r="I687" t="n">
-        <v>0.3357</v>
+        <v>0.3353</v>
       </c>
       <c r="J687" t="n">
-        <v>8.056800000000001</v>
+        <v>8.0472</v>
       </c>
     </row>
     <row r="688">
@@ -31706,13 +31706,13 @@
         <v>24</v>
       </c>
       <c r="H688" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I688" t="n">
-        <v>0.1036</v>
+        <v>0.1218</v>
       </c>
       <c r="J688" t="n">
-        <v>2.4864</v>
+        <v>2.9232</v>
       </c>
     </row>
     <row r="689">
@@ -31749,10 +31749,10 @@
         <v>1.04</v>
       </c>
       <c r="I689" t="n">
-        <v>0.1036</v>
+        <v>0.1033</v>
       </c>
       <c r="J689" t="n">
-        <v>2.4864</v>
+        <v>2.4792</v>
       </c>
     </row>
     <row r="690">
@@ -31789,10 +31789,10 @@
         <v>0.98</v>
       </c>
       <c r="I690" t="n">
-        <v>-0.0401</v>
+        <v>-0.0402</v>
       </c>
       <c r="J690" t="n">
-        <v>-0.9624</v>
+        <v>-0.9648</v>
       </c>
     </row>
     <row r="691">
@@ -31829,10 +31829,10 @@
         <v>0.51</v>
       </c>
       <c r="I691" t="n">
-        <v>-0.5108</v>
+        <v>-0.511</v>
       </c>
       <c r="J691" t="n">
-        <v>-12.2592</v>
+        <v>-12.264</v>
       </c>
     </row>
     <row r="692">
@@ -33866,13 +33866,13 @@
         <v>21</v>
       </c>
       <c r="H742" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I742" t="n">
-        <v>1.5306</v>
+        <v>1.5414</v>
       </c>
       <c r="J742" t="n">
-        <v>32.1426</v>
+        <v>32.3694</v>
       </c>
     </row>
     <row r="743">
@@ -33909,10 +33909,10 @@
         <v>1.51</v>
       </c>
       <c r="I743" t="n">
-        <v>1.0889</v>
+        <v>1.0881</v>
       </c>
       <c r="J743" t="n">
-        <v>22.8669</v>
+        <v>22.8501</v>
       </c>
     </row>
     <row r="744">
@@ -33946,13 +33946,13 @@
         <v>21</v>
       </c>
       <c r="H744" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I744" t="n">
-        <v>0.8832</v>
+        <v>0.9008</v>
       </c>
       <c r="J744" t="n">
-        <v>18.5472</v>
+        <v>18.9168</v>
       </c>
     </row>
     <row r="745">
@@ -33986,13 +33986,13 @@
         <v>21</v>
       </c>
       <c r="H745" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I745" t="n">
-        <v>0.3348</v>
+        <v>0.3587</v>
       </c>
       <c r="J745" t="n">
-        <v>7.0308</v>
+        <v>7.5327</v>
       </c>
     </row>
     <row r="746">
@@ -34029,10 +34029,10 @@
         <v>0.96</v>
       </c>
       <c r="I746" t="n">
-        <v>-0.2325</v>
+        <v>-0.2334</v>
       </c>
       <c r="J746" t="n">
-        <v>-4.8825</v>
+        <v>-4.9014</v>
       </c>
     </row>
     <row r="747">
@@ -35269,10 +35269,10 @@
         <v>0.89</v>
       </c>
       <c r="I777" t="n">
-        <v>-0.1021</v>
+        <v>-0.1028</v>
       </c>
       <c r="J777" t="n">
-        <v>-1.5315</v>
+        <v>-1.542</v>
       </c>
     </row>
     <row r="778">
@@ -35306,13 +35306,13 @@
         <v>15</v>
       </c>
       <c r="H778" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I778" t="n">
-        <v>-0.1265</v>
+        <v>-0.1151</v>
       </c>
       <c r="J778" t="n">
-        <v>-1.8975</v>
+        <v>-1.7265</v>
       </c>
     </row>
     <row r="779">
@@ -35349,10 +35349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I779" t="n">
-        <v>-0.4307</v>
+        <v>-0.4309</v>
       </c>
       <c r="J779" t="n">
-        <v>-6.4605</v>
+        <v>-6.4635</v>
       </c>
     </row>
     <row r="780">
@@ -35389,10 +35389,10 @@
         <v>0.44</v>
       </c>
       <c r="I780" t="n">
-        <v>-0.5362</v>
+        <v>-0.5365</v>
       </c>
       <c r="J780" t="n">
-        <v>-8.042999999999999</v>
+        <v>-8.047499999999999</v>
       </c>
     </row>
     <row r="781">
@@ -35429,10 +35429,10 @@
         <v>0.35</v>
       </c>
       <c r="I781" t="n">
-        <v>-0.6153</v>
+        <v>-0.6155</v>
       </c>
       <c r="J781" t="n">
-        <v>-9.2295</v>
+        <v>-9.2325</v>
       </c>
     </row>
     <row r="782">
@@ -35466,13 +35466,13 @@
         <v>23</v>
       </c>
       <c r="H782" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I782" t="n">
-        <v>0.5851</v>
+        <v>0.5964</v>
       </c>
       <c r="J782" t="n">
-        <v>13.4573</v>
+        <v>13.7172</v>
       </c>
     </row>
     <row r="783">
@@ -35509,10 +35509,10 @@
         <v>1.24</v>
       </c>
       <c r="I783" t="n">
-        <v>0.3989</v>
+        <v>0.3984</v>
       </c>
       <c r="J783" t="n">
-        <v>9.1747</v>
+        <v>9.1632</v>
       </c>
     </row>
     <row r="784">
@@ -35549,10 +35549,10 @@
         <v>0.91</v>
       </c>
       <c r="I784" t="n">
-        <v>-0.1328</v>
+        <v>-0.1329</v>
       </c>
       <c r="J784" t="n">
-        <v>-3.0544</v>
+        <v>-3.0567</v>
       </c>
     </row>
     <row r="785">
@@ -35589,10 +35589,10 @@
         <v>0.71</v>
       </c>
       <c r="I785" t="n">
-        <v>-0.3355</v>
+        <v>-0.3357</v>
       </c>
       <c r="J785" t="n">
-        <v>-7.7165</v>
+        <v>-7.7211</v>
       </c>
     </row>
     <row r="786">
@@ -35629,10 +35629,10 @@
         <v>0.59</v>
       </c>
       <c r="I786" t="n">
-        <v>-0.4433</v>
+        <v>-0.4435</v>
       </c>
       <c r="J786" t="n">
-        <v>-10.1959</v>
+        <v>-10.2005</v>
       </c>
     </row>
     <row r="787">
@@ -36866,13 +36866,13 @@
         <v>23</v>
       </c>
       <c r="H817" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I817" t="n">
-        <v>0.8465</v>
+        <v>0.8595</v>
       </c>
       <c r="J817" t="n">
-        <v>19.4695</v>
+        <v>19.7685</v>
       </c>
     </row>
     <row r="818">
@@ -36906,13 +36906,13 @@
         <v>23</v>
       </c>
       <c r="H818" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I818" t="n">
-        <v>0.6105</v>
+        <v>0.6248</v>
       </c>
       <c r="J818" t="n">
-        <v>14.0415</v>
+        <v>14.3704</v>
       </c>
     </row>
     <row r="819">
@@ -36949,10 +36949,10 @@
         <v>0.96</v>
       </c>
       <c r="I819" t="n">
-        <v>-0.078</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J819" t="n">
-        <v>-1.794</v>
+        <v>-1.8009</v>
       </c>
     </row>
     <row r="820">
@@ -36989,10 +36989,10 @@
         <v>0.83</v>
       </c>
       <c r="I820" t="n">
-        <v>-0.2284</v>
+        <v>-0.2287</v>
       </c>
       <c r="J820" t="n">
-        <v>-5.2532</v>
+        <v>-5.2601</v>
       </c>
     </row>
     <row r="821">
@@ -37029,10 +37029,10 @@
         <v>0.76</v>
       </c>
       <c r="I821" t="n">
-        <v>-0.2975</v>
+        <v>-0.2978</v>
       </c>
       <c r="J821" t="n">
-        <v>-6.8425</v>
+        <v>-6.8494</v>
       </c>
     </row>
     <row r="822">
@@ -38669,10 +38669,10 @@
         <v>1.25</v>
       </c>
       <c r="I862" t="n">
-        <v>0.6631</v>
+        <v>0.6623</v>
       </c>
       <c r="J862" t="n">
-        <v>15.2513</v>
+        <v>15.2329</v>
       </c>
     </row>
     <row r="863">
@@ -38706,13 +38706,13 @@
         <v>23</v>
       </c>
       <c r="H863" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I863" t="n">
-        <v>0.6202</v>
+        <v>0.6409</v>
       </c>
       <c r="J863" t="n">
-        <v>14.2646</v>
+        <v>14.7407</v>
       </c>
     </row>
     <row r="864">
@@ -38746,13 +38746,13 @@
         <v>23</v>
       </c>
       <c r="H864" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I864" t="n">
-        <v>0.5985</v>
+        <v>0.6194</v>
       </c>
       <c r="J864" t="n">
-        <v>13.7655</v>
+        <v>14.2462</v>
       </c>
     </row>
     <row r="865">
@@ -38789,10 +38789,10 @@
         <v>1.04</v>
       </c>
       <c r="I865" t="n">
-        <v>0.1495</v>
+        <v>0.1489</v>
       </c>
       <c r="J865" t="n">
-        <v>3.4385</v>
+        <v>3.4247</v>
       </c>
     </row>
     <row r="866">
@@ -38829,10 +38829,10 @@
         <v>0.92</v>
       </c>
       <c r="I866" t="n">
-        <v>-0.3132</v>
+        <v>-0.3139</v>
       </c>
       <c r="J866" t="n">
-        <v>-7.2036</v>
+        <v>-7.2197</v>
       </c>
     </row>
     <row r="867">
@@ -41866,13 +41866,13 @@
         <v>16</v>
       </c>
       <c r="H942" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I942" t="n">
-        <v>1.5351</v>
+        <v>1.5466</v>
       </c>
       <c r="J942" t="n">
-        <v>24.5616</v>
+        <v>24.7456</v>
       </c>
     </row>
     <row r="943">
@@ -41909,10 +41909,10 @@
         <v>1.59</v>
       </c>
       <c r="I943" t="n">
-        <v>1.1801</v>
+        <v>1.1799</v>
       </c>
       <c r="J943" t="n">
-        <v>18.8816</v>
+        <v>18.8784</v>
       </c>
     </row>
     <row r="944">
@@ -41949,10 +41949,10 @@
         <v>1.38</v>
       </c>
       <c r="I944" t="n">
-        <v>0.8738</v>
+        <v>0.8736</v>
       </c>
       <c r="J944" t="n">
-        <v>13.9808</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="945">
@@ -41989,10 +41989,10 @@
         <v>1.27</v>
       </c>
       <c r="I945" t="n">
-        <v>0.6582</v>
+        <v>0.6579</v>
       </c>
       <c r="J945" t="n">
-        <v>10.5312</v>
+        <v>10.5264</v>
       </c>
     </row>
     <row r="946">
@@ -42029,10 +42029,10 @@
         <v>1.18</v>
       </c>
       <c r="I946" t="n">
-        <v>0.4638</v>
+        <v>0.4635</v>
       </c>
       <c r="J946" t="n">
-        <v>7.4208</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="947">
